--- a/docs/test-cases/SPM-31_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-31_Test_Cases.xlsx
@@ -4,25 +4,26 @@
   <workbookPr/>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TC01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TC02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TC03" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TC04" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TC05" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TC06" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TC07" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TC08" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TC09" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TC10" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TC11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="TC13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="TC14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="TC15" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="TC16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="TC17" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="TC18" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="TC19" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TC03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TC04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TC06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TC07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TC08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TC09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TC10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TC11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TC16" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="TC17" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TC18" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TC19" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -169,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -265,6 +266,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,12 +563,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="35">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>SPM-31: As an authorised user (Event Coordinator, Event Organiser, or other role with access to the event), I want to view an event's current information so that I can plan around or track accurate, up-to-date details</t>
         </is>
@@ -573,32 +580,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="38" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="38" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="38" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -625,27 +632,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC01</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>Assigned coordinator views full event details on the Overview tab</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -664,27 +671,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC02</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>A role with no ownership of the event can still view its Overview tab</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -703,27 +710,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC03</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>Opening a draft from 'My Events' goes straight to the draft editor, never the Overview tab</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -742,27 +749,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC04</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>Organiser views a colleague's already-submitted event from the same client organisation</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -781,27 +788,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC05</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>Organiser cannot view a colleague's draft, even within the same organisation</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="39" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -820,27 +827,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC06</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>Organiser cannot view another client's event at all</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="39" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -859,27 +866,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC07</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>Attendee cannot view an event that has not yet been confirmed</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="39" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -898,27 +905,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC08</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>Attendee cannot view a confirmed event that isn't open for registration</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="39" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -937,27 +944,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC09</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>Attendee viewing a confirmed, registration-open event sees its public details</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -976,27 +983,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC10</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>A signed-out visitor is sent to log in when opening an event directly</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="39" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1015,27 +1022,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC11</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="39" t="inlineStr">
         <is>
           <t>Opening an event that doesn't exist shows a clear message rather than an error page</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="39" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1054,27 +1061,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC12</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="39" t="inlineStr">
         <is>
           <t>Organiser sees the assigned coordinator's name tagged to their event on the Overview tab</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1093,27 +1100,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC13</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="39" t="inlineStr">
         <is>
           <t>Overview tab shows 'Not yet assigned' when an event has no coordinator</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="39" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1132,27 +1139,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC14</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>Attendee's Overview view shows the company but never the organiser's name or the coordinator</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="39" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="39" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1171,27 +1178,27 @@
           <t>TC15</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC15</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="39" t="inlineStr">
         <is>
           <t>Navigating directly to a draft's Overview address redirects to the draft editor instead</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="39" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1210,27 +1217,27 @@
           <t>TC16</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC16</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="39" t="inlineStr">
         <is>
           <t>Every event shows a distinct, auto-generated reference number</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1249,27 +1256,27 @@
           <t>TC17</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC17</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="39" t="inlineStr">
         <is>
           <t>An event's web address uses its reference number, not an internal id</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1288,27 +1295,27 @@
           <t>TC18</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC18</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="39" t="inlineStr">
         <is>
           <t>'All Events' shows each event's reference number as its own column</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="39" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="39" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1324,19 +1331,19 @@
     <row r="22" ht="15.75" customHeight="1" s="35"/>
     <row r="23" ht="15.75" customHeight="1" s="35"/>
     <row r="24" ht="15.75" customHeight="1" s="35">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C24" s="36" t="n"/>
       <c r="D24" s="37" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="38" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1344,19 +1351,19 @@
       <c r="F24" s="37" t="n"/>
     </row>
     <row r="25" ht="246.75" customHeight="1" s="35">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="39" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Authorised users can view the event's current information.</t>
         </is>
       </c>
       <c r="C25" s="36" t="n"/>
       <c r="D25" s="37" t="n"/>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="39" t="inlineStr">
         <is>
           <t>SPM-31-TC01
 SPM-31-TC02
@@ -1382,12 +1389,12 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" s="35"/>
     <row r="27" ht="206.25" customHeight="1" s="35">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>prisma/schema.prisma
 prisma/seed.ts
@@ -2424,7 +2431,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="35" min="1" max="1"/>
@@ -2446,26 +2453,26 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.25" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>Logged in as Tom Harris (tom.harris@example.com / password123), Attendee.
- 'Meridian Wealth Management Forum' has status Confirmed and registration enabled (capacity 150) — the one case where an Attendee is meant to be authorised to view an event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="35">
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Harbourline Claims Systems Training' has status Confirmed but registration is not enabled for it, coordinator Priya Raj.
+ Anita Devi (anita.devi@example.com / password123) is an Attendee. Registration isn't open, so this event never appears in her 'Browse Events' list — the address below has to come from somewhere else, e.g. forwarded by staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2473,7 +2480,9 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>1. Open 'Meridian Wealth Management Forum' event</t>
+          <t>1. Logged in as Priya Raj (priya.raj@connectsphere.com / password123), open 'Harbourline Claims Systems Training' and note its web address
+ 2. Log out and log in as Anita Devi (anita.devi@example.com / password123)
+ 3. Navigate directly to that web address</t>
         </is>
       </c>
     </row>
@@ -2485,11 +2494,11 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Event: Meridian Wealth Management Forum (Confirmed, registration enabled) | Viewer role: Attendee</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="206.25" customHeight="1" s="35">
+          <t>Event: Harbourline Claims Systems Training (Confirmed, registration not enabled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2497,10 +2506,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>A reference such as 'EVT-000005' is shown next to the title, the same as for every other role.
- The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
- There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
- The 'Registration' card shows Capacity and the registration window.</t>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — being Confirmed is not enough on its own; the event must also be open for registration for an Attendee to view it.</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2516,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2544,10 +2550,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>A reference such as 'EVT-000005' is shown next to the title, the same as for every other role.
- The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
- There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
- The 'Registration' card shows Capacity and the registration window.</t>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — being Confirmed is not enough on its own; the event must also be open for registration for an Attendee to view it.</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2584,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -2615,10 +2618,7 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>A reference such as 'EVT-000200' is shown next to the title, the same as for every other role.
- The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
- There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
- The 'Registration' card shows Capacity and the registration window.</t>
+          <t>The page shows 'Could not load this', 'This event doesn't exist, or you don't have access to it.' — being Confirmed is not enough on its own; the event must also be open for registration for an Attendee to view it.</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>EVT-000200 shown instead of EVT-000005</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2670,75 +2670,12 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" s="35"/>
     <row r="25" ht="15.75" customHeight="1" s="35"/>
-    <row r="26" ht="15.75" customHeight="1" s="35">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="35">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A reference such as 'EVT-000005' is shown next to the title, the same as for every other role.
- The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
- There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
- The 'Registration' card shows Capacity and the registration window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="35">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="35">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>Failed cases fixed by Kristen on 2026-09-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="35">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="35">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="n">
-        <v>46290</v>
-      </c>
-    </row>
+    <row r="26" ht="15.75" customHeight="1" s="35"/>
+    <row r="27" ht="15.75" customHeight="1" s="35"/>
+    <row r="28" ht="15.75" customHeight="1" s="35"/>
+    <row r="29" ht="15.75" customHeight="1" s="35"/>
+    <row r="30" ht="15.75" customHeight="1" s="35"/>
+    <row r="31" ht="15.75" customHeight="1" s="35"/>
     <row r="32" ht="15.75" customHeight="1" s="35"/>
     <row r="33" ht="15.75" customHeight="1" s="35"/>
     <row r="34" ht="15.75" customHeight="1" s="35"/>
@@ -3720,7 +3657,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="35" min="1" max="1"/>
@@ -3742,22 +3679,22 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>No one is logged in (signed out).
-'Meridian Wealth Management Forum' exists and is Confirmed.</t>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Logged in as Tom Harris (tom.harris@example.com / password123), Attendee.
+ 'Meridian Wealth Management Forum' has status Confirmed and registration enabled (capacity 150) — the one case where an Attendee is meant to be authorised to view an event.</t>
         </is>
       </c>
     </row>
@@ -3767,33 +3704,36 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Navigate directly to the web address for 'Meridian Wealth Management Forum' while signed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="35">
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1. Open 'Meridian Wealth Management Forum' event</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Session: signed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1" s="35">
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Event: Meridian Wealth Management Forum (Confirmed, registration enabled) | Viewer role: Attendee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="206.25" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The browser is redirected to the login page rather than showing any event information.</t>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000005' is shown next to the title, the same as for every other role.
+ The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
+ There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
+ The 'Registration' card shows Capacity and the registration window.</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3743,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3835,9 +3775,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The browser is redirected to the login page rather than showing any event information.</t>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000005' is shown next to the title, the same as for every other role.
+ The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
+ There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
+ The 'Registration' card shows Capacity and the registration window.</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3814,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3903,9 +3846,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The browser is redirected to the login page rather than showing any event information.</t>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000200' is shown next to the title, the same as for every other role.
+ The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
+ There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
+ The 'Registration' card shows Capacity and the registration window.</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3863,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3875,7 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>EVT-000200 shown instead of EVT-000005</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3885,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -3957,12 +3903,75 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" s="35"/>
     <row r="25" ht="15.75" customHeight="1" s="35"/>
-    <row r="26" ht="15.75" customHeight="1" s="35"/>
-    <row r="27" ht="15.75" customHeight="1" s="35"/>
-    <row r="28" ht="15.75" customHeight="1" s="35"/>
-    <row r="29" ht="15.75" customHeight="1" s="35"/>
-    <row r="30" ht="15.75" customHeight="1" s="35"/>
-    <row r="31" ht="15.75" customHeight="1" s="35"/>
+    <row r="26" ht="15.75" customHeight="1" s="35">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="35">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000005' is shown next to the title, the same as for every other role.
+ The Overview page loads and shows a curated 'Details' card: Category, Status, When, Description, and Company — nothing else.
+ There is no 'Venue requirements' card at all, and no 'Expected attendance', 'Preferred layout', 'Organiser' or 'Coordinator' row — those are omitted entirely rather than shown blank, since none of that is internal planning information or relevant to deciding whether to register.
+ The 'Registration' card shows Capacity and the registration window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="35">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="35">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Failed cases fixed by Kristen on 2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="35">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="35">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>46290</v>
+      </c>
+    </row>
     <row r="32" ht="15.75" customHeight="1" s="35"/>
     <row r="33" ht="15.75" customHeight="1" s="35"/>
     <row r="34" ht="15.75" customHeight="1" s="35"/>
@@ -4966,9 +4975,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC11</t>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC10</t>
         </is>
       </c>
     </row>
@@ -4978,22 +4987,22 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>No one is logged in (signed out).
+'Meridian Wealth Management Forum' exists and is Confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Edit the web address of any event page to use a reference that doesn't exist, e.g. EVT-999999
-2. Load that address</t>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Navigate directly to the web address for 'Meridian Wealth Management Forum' while signed out</t>
         </is>
       </c>
     </row>
@@ -5003,21 +5012,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event reference: EVT-999999 (does not exist)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="35">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Session: signed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.' with a 'Retry' option — not a crash or a raw error page.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The browser is redirected to the login page rather than showing any event information.</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5036,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5059,9 +5068,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.' with a 'Retry' option — not a crash or a raw error page.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The browser is redirected to the login page rather than showing any event information.</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5104,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -5127,9 +5136,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The page shows 'Could not load this','This event doesn't exist, or you don't have access to it.' with a 'Retry' option — not a crash or a raw error page.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The browser is redirected to the login page rather than showing any event information.</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5172,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6190,59 +6199,58 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="57.75" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as James Koh (james.koh@meridianfina.com / password123), Event Organiser.
-'Meridian Wealth Management Forum' (his event) has Daniel Tan assigned as its coordinator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open 'My Events'
-2. Open 'Meridian Wealth Management Forum'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="35">
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Edit the web address of any event page to use a reference that doesn't exist, e.g. EVT-999999
+2. Load that address</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Meridian Wealth Management Forum | Coordinator: Daniel Tan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1" s="35">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event reference: EVT-999999 (does not exist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The Overview tab shows 'Coordinator: Daniel Tan' tagged to the event.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.' with a 'Retry' option — not a crash or a raw error page.</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6260,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6284,9 +6292,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The Overview tab shows 'Coordinator: Daniel Tan' tagged to the event.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.' with a 'Retry' option — not a crash or a raw error page.</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6328,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6352,9 +6360,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The Overview tab shows 'Coordinator: Daniel Tan' tagged to the event.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The page shows 'Could not load this','This event doesn't exist, or you don't have access to it.' with a 'Retry' option — not a crash or a raw error page.</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6396,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -7415,9 +7423,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC13</t>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC12</t>
         </is>
       </c>
     </row>
@@ -7427,10 +7435,10 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>Logged in as James Koh (james.koh@meridianfina.com / password123), Event Organiser.
-'Meridian Graduate Recruitment Evening' (his event) has status Submitted and no coordinator assigned yet.</t>
+'Meridian Wealth Management Forum' (his event) has Daniel Tan assigned as its coordinator.</t>
         </is>
       </c>
     </row>
@@ -7440,10 +7448,10 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>1. Open 'My Events'
-2. Open 'Meridian Graduate Recruitment Evening'</t>
+2. Open 'Meridian Wealth Management Forum'</t>
         </is>
       </c>
     </row>
@@ -7453,9 +7461,9 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Meridian Graduate Recruitment Evening (no coordinator)</t>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Meridian Wealth Management Forum | Coordinator: Daniel Tan</t>
         </is>
       </c>
     </row>
@@ -7465,9 +7473,9 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The Overview tab shows 'Coordinator: Not yet assigned' rather than a blank field.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The Overview tab shows 'Coordinator: Daniel Tan' tagged to the event.</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7485,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7509,9 +7517,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The Overview tab shows 'Coordinator: Not yet assigned' rather than a blank field.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The Overview tab shows 'Coordinator: Daniel Tan' tagged to the event.</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7553,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7577,9 +7585,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The Overview tab shows 'Coordinator: Not yet assigned' rather than a blank field.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The Overview tab shows 'Coordinator: Daniel Tan' tagged to the event.</t>
         </is>
       </c>
     </row>
@@ -7613,7 +7621,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -8640,22 +8648,22 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.25" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="57.75" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>Logged in as Tom Harris (tom.harris@example.com / password123), Attendee.
- 'Meridian Wealth Management Forum' has status Confirmed, registration enabled, organiser James Koh, company Meridian Financial Group, and Daniel Tan assigned as coordinator.</t>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as James Koh (james.koh@meridianfina.com / password123), Event Organiser.
+'Meridian Graduate Recruitment Evening' (his event) has status Submitted and no coordinator assigned yet.</t>
         </is>
       </c>
     </row>
@@ -8665,9 +8673,10 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>1. Open 'Meridian Wealth Management Forum' from 'Browse Events'</t>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Open 'My Events'
+2. Open 'Meridian Graduate Recruitment Evening'</t>
         </is>
       </c>
     </row>
@@ -8677,22 +8686,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Event: Meridian Wealth Management Forum | Viewer role: Attendee</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.25" customHeight="1" s="35">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Meridian Graduate Recruitment Evening (no coordinator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>A 'Company' row reads 'Meridian Financial Group'.
- No 'Organiser' row and no 'Coordinator' row or label appear anywhere on the page, and there is no 'Venue requirements' card at all — who personally raised the request, who is coordinating it, and the venue/facility arrangements all stay internal planning information, hidden from the public, even though the company running it, the coordinator's/organiser's name, and the venue requirements are now all shown to internal roles and the Organiser themselves.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The Overview tab shows 'Coordinator: Not yet assigned' rather than a blank field.</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8710,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8734,10 +8742,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A 'Company' row reads 'Meridian Financial Group'.
- No 'Organiser' row and no 'Coordinator' row or label appear anywhere on the page, and there is no 'Venue requirements' card at all — who personally raised the request, who is coordinating it, and the venue/facility arrangements all stay internal planning information, hidden from the public, even though the company running it, the coordinator's/organiser's name, and the venue requirements are now all shown to internal roles and the Organiser themselves.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The Overview tab shows 'Coordinator: Not yet assigned' rather than a blank field.</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8778,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8803,10 +8810,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A 'Company' row reads 'Meridian Financial Group'.
- No 'Organiser' row and no 'Coordinator' row or label appear anywhere on the page, and there is no 'Venue requirements' card at all — who personally raised the request, who is coordinating it, and the venue/facility arrangements all stay internal planning information, hidden from the public, even though the company running it, the coordinator's/organiser's name, and the venue requirements are now all shown to internal roles and the Organiser themselves.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The Overview tab shows 'Coordinator: Not yet assigned' rather than a blank field.</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8846,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -9867,59 +9873,59 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.25" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), Event Organiser.
-'Q1 Investor Update (rough idea)' is her own Draft event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="35">
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Logged in as Tom Harris (tom.harris@example.com / password123), Attendee.
+ 'Meridian Wealth Management Forum' has status Confirmed, registration enabled, organiser James Koh, company Meridian Financial Group, and Daniel Tan assigned as coordinator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Type the Overview web address for 'Q1 Investor Update (rough idea)' directly into the browser (the plain event address, not '/edit')</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="35">
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1. Open 'Meridian Wealth Management Forum' from 'Browse Events'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Q1 Investor Update (rough idea) (Draft)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="84.75" customHeight="1" s="35">
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Event: Meridian Wealth Management Forum | Viewer role: Attendee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.25" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The browser is immediately redirected to the 'Edit draft' page for that event.
-The Overview tab's Details card, draft info banner, and Organiser/Company/Coordinator rows are never shown, even briefly — there is no Overview view for a draft, reachable by any address.</t>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>A 'Company' row reads 'Meridian Financial Group'.
+ No 'Organiser' row and no 'Coordinator' row or label appear anywhere on the page, and there is no 'Venue requirements' card at all — who personally raised the request, who is coordinating it, and the venue/facility arrangements all stay internal planning information, hidden from the public, even though the company running it, the coordinator's/organiser's name, and the venue requirements are now all shown to internal roles and the Organiser themselves.</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9935,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -9961,10 +9967,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The browser is immediately redirected to the 'Edit draft' page for that event.
-The Overview tab's Details card, draft info banner, and Organiser/Company/Coordinator rows are never shown, even briefly — there is no Overview view for a draft, reachable by any address.</t>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>A 'Company' row reads 'Meridian Financial Group'.
+ No 'Organiser' row and no 'Coordinator' row or label appear anywhere on the page, and there is no 'Venue requirements' card at all — who personally raised the request, who is coordinating it, and the venue/facility arrangements all stay internal planning information, hidden from the public, even though the company running it, the coordinator's/organiser's name, and the venue requirements are now all shown to internal roles and the Organiser themselves.</t>
         </is>
       </c>
     </row>
@@ -9998,7 +10004,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -10030,10 +10036,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The browser is immediately redirected to the 'Edit draft' page for that event.
-The Overview tab's Details card, draft info banner, and Organiser/Company/Coordinator rows are never shown, even briefly — there is no Overview view for a draft, reachable by any address.</t>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>A 'Company' row reads 'Meridian Financial Group'.
+ No 'Organiser' row and no 'Coordinator' row or label appear anywhere on the page, and there is no 'Venue requirements' card at all — who personally raised the request, who is coordinating it, and the venue/facility arrangements all stay internal planning information, hidden from the public, even though the company running it, the coordinator's/organiser's name, and the venue requirements are now all shown to internal roles and the Organiser themselves.</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10073,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -11094,61 +11100,59 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="57.75" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Priya Raj (priya.raj@connectsphere.com / password123), Event Coordinator.
-'Kirana Regional Managers Offsite' and 'Straits Medical Research Symposium' are two different, already-submitted events.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), Event Organiser.
+'Q1 Investor Update (rough idea)' is her own Draft event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open 'All Events'
-2. Open 'Kirana Regional Managers Offsite' and note the reference shown next to its title
-3. Go back and open 'Straits Medical Research Symposium' and note its reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="35">
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Type the Overview web address for 'Q1 Investor Update (rough idea)' directly into the browser (the plain event address, not '/edit')</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Events: Kirana Regional Managers Offsite, Straits Medical Research Symposium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="35">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Q1 Investor Update (rough idea) (Draft)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="84.75" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Each event shows its own reference in the form 'EVT-######' next to its title, beside the status badge.
-The two events show two different references — the number is specific to that event, not a shared or repeated value.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The browser is immediately redirected to the 'Edit draft' page for that event.
+The Overview tab's Details card, draft info banner, and Organiser/Company/Coordinator rows are never shown, even briefly — there is no Overview view for a draft, reachable by any address.</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11162,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -11190,10 +11194,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Each event shows its own reference in the form 'EVT-######' next to its title, beside the status badge.
-The two events show two different references — the number is specific to that event, not a shared or repeated value.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The browser is immediately redirected to the 'Edit draft' page for that event.
+The Overview tab's Details card, draft info banner, and Organiser/Company/Coordinator rows are never shown, even briefly — there is no Overview view for a draft, reachable by any address.</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11231,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -11259,10 +11263,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Each event shows its own reference in the form 'EVT-######' next to its title, beside the status badge.
-The two events show two different references — the number is specific to that event, not a shared or repeated value.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The browser is immediately redirected to the 'Edit draft' page for that event.
+The Overview tab's Details card, draft info banner, and Organiser/Company/Coordinator rows are never shown, even briefly — there is no Overview view for a draft, reachable by any address.</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11300,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -12301,1295 +12305,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col width="24.75" customWidth="1" style="35" min="1" max="1"/>
-    <col width="56.75" customWidth="1" style="35" min="2" max="2"/>
-    <col width="12.63" customWidth="1" style="35" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="35">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="35">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.25" customHeight="1" s="35">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator assigned to 'Meridian Wealth Management Forum' (reference EVT-000005).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="35">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open 'All Events'
-2. Open 'Meridian Wealth Management Forum'
-3. Look at the web address shown in the browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="35">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Meridian Wealth Management Forum (EVT-000005)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="35">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The web address ends in '/EVT-000005' — a reference a person could read aloud or type from memory, not a long opaque id.
-Opening that same address directly (typed or bookmarked) loads the same event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" s="35">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" s="35">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" s="35"/>
-    <row r="10" ht="15.75" customHeight="1" s="35">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="35">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The web address ends in '/EVT-000005' — a reference a person could read aloud or type from memory, not a long opaque id.
-Opening that same address directly (typed or bookmarked) loads the same event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" s="35">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="35">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="35">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Kristen</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="35">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="35"/>
-    <row r="17" ht="15.75" customHeight="1" s="35"/>
-    <row r="18" ht="15.75" customHeight="1" s="35">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="35">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The web address ends in '/EVT-000200' — a reference a person could read aloud or type from memory, not a long opaque id.
-Opening that same address directly (typed or bookmarked) loads the same event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="35">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="35">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>EVT-000200 shown instead of EVT-000005</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="35">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="35">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="35"/>
-    <row r="25" ht="15.75" customHeight="1" s="35"/>
-    <row r="26" ht="15.75" customHeight="1" s="35">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" s="35">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>The web address ends in '/EVT-000005' — a reference a person could read aloud or type from memory, not a long opaque id.
-Opening that same address directly (typed or bookmarked) loads the same event.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" s="35">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="35">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>Failed cases were fixed by Kristen on 2026-09-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="35">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" s="35">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="n">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" s="35"/>
-    <row r="33" ht="15.75" customHeight="1" s="35"/>
-    <row r="34" ht="15.75" customHeight="1" s="35"/>
-    <row r="35" ht="15.75" customHeight="1" s="35"/>
-    <row r="36" ht="15.75" customHeight="1" s="35"/>
-    <row r="37" ht="15.75" customHeight="1" s="35"/>
-    <row r="38" ht="15.75" customHeight="1" s="35"/>
-    <row r="39" ht="15.75" customHeight="1" s="35"/>
-    <row r="40" ht="15.75" customHeight="1" s="35"/>
-    <row r="41" ht="15.75" customHeight="1" s="35"/>
-    <row r="42" ht="15.75" customHeight="1" s="35"/>
-    <row r="43" ht="15.75" customHeight="1" s="35"/>
-    <row r="44" ht="15.75" customHeight="1" s="35"/>
-    <row r="45" ht="15.75" customHeight="1" s="35"/>
-    <row r="46" ht="15.75" customHeight="1" s="35"/>
-    <row r="47" ht="15.75" customHeight="1" s="35"/>
-    <row r="48" ht="15.75" customHeight="1" s="35"/>
-    <row r="49" ht="15.75" customHeight="1" s="35"/>
-    <row r="50" ht="15.75" customHeight="1" s="35"/>
-    <row r="51" ht="15.75" customHeight="1" s="35"/>
-    <row r="52" ht="15.75" customHeight="1" s="35"/>
-    <row r="53" ht="15.75" customHeight="1" s="35"/>
-    <row r="54" ht="15.75" customHeight="1" s="35"/>
-    <row r="55" ht="15.75" customHeight="1" s="35"/>
-    <row r="56" ht="15.75" customHeight="1" s="35"/>
-    <row r="57" ht="15.75" customHeight="1" s="35"/>
-    <row r="58" ht="15.75" customHeight="1" s="35"/>
-    <row r="59" ht="15.75" customHeight="1" s="35"/>
-    <row r="60" ht="15.75" customHeight="1" s="35"/>
-    <row r="61" ht="15.75" customHeight="1" s="35"/>
-    <row r="62" ht="15.75" customHeight="1" s="35"/>
-    <row r="63" ht="15.75" customHeight="1" s="35"/>
-    <row r="64" ht="15.75" customHeight="1" s="35"/>
-    <row r="65" ht="15.75" customHeight="1" s="35"/>
-    <row r="66" ht="15.75" customHeight="1" s="35"/>
-    <row r="67" ht="15.75" customHeight="1" s="35"/>
-    <row r="68" ht="15.75" customHeight="1" s="35"/>
-    <row r="69" ht="15.75" customHeight="1" s="35"/>
-    <row r="70" ht="15.75" customHeight="1" s="35"/>
-    <row r="71" ht="15.75" customHeight="1" s="35"/>
-    <row r="72" ht="15.75" customHeight="1" s="35"/>
-    <row r="73" ht="15.75" customHeight="1" s="35"/>
-    <row r="74" ht="15.75" customHeight="1" s="35"/>
-    <row r="75" ht="15.75" customHeight="1" s="35"/>
-    <row r="76" ht="15.75" customHeight="1" s="35"/>
-    <row r="77" ht="15.75" customHeight="1" s="35"/>
-    <row r="78" ht="15.75" customHeight="1" s="35"/>
-    <row r="79" ht="15.75" customHeight="1" s="35"/>
-    <row r="80" ht="15.75" customHeight="1" s="35"/>
-    <row r="81" ht="15.75" customHeight="1" s="35"/>
-    <row r="82" ht="15.75" customHeight="1" s="35"/>
-    <row r="83" ht="15.75" customHeight="1" s="35"/>
-    <row r="84" ht="15.75" customHeight="1" s="35"/>
-    <row r="85" ht="15.75" customHeight="1" s="35"/>
-    <row r="86" ht="15.75" customHeight="1" s="35"/>
-    <row r="87" ht="15.75" customHeight="1" s="35"/>
-    <row r="88" ht="15.75" customHeight="1" s="35"/>
-    <row r="89" ht="15.75" customHeight="1" s="35"/>
-    <row r="90" ht="15.75" customHeight="1" s="35"/>
-    <row r="91" ht="15.75" customHeight="1" s="35"/>
-    <row r="92" ht="15.75" customHeight="1" s="35"/>
-    <row r="93" ht="15.75" customHeight="1" s="35"/>
-    <row r="94" ht="15.75" customHeight="1" s="35"/>
-    <row r="95" ht="15.75" customHeight="1" s="35"/>
-    <row r="96" ht="15.75" customHeight="1" s="35"/>
-    <row r="97" ht="15.75" customHeight="1" s="35"/>
-    <row r="98" ht="15.75" customHeight="1" s="35"/>
-    <row r="99" ht="15.75" customHeight="1" s="35"/>
-    <row r="100" ht="15.75" customHeight="1" s="35"/>
-    <row r="101" ht="15.75" customHeight="1" s="35"/>
-    <row r="102" ht="15.75" customHeight="1" s="35"/>
-    <row r="103" ht="15.75" customHeight="1" s="35"/>
-    <row r="104" ht="15.75" customHeight="1" s="35"/>
-    <row r="105" ht="15.75" customHeight="1" s="35"/>
-    <row r="106" ht="15.75" customHeight="1" s="35"/>
-    <row r="107" ht="15.75" customHeight="1" s="35"/>
-    <row r="108" ht="15.75" customHeight="1" s="35"/>
-    <row r="109" ht="15.75" customHeight="1" s="35"/>
-    <row r="110" ht="15.75" customHeight="1" s="35"/>
-    <row r="111" ht="15.75" customHeight="1" s="35"/>
-    <row r="112" ht="15.75" customHeight="1" s="35"/>
-    <row r="113" ht="15.75" customHeight="1" s="35"/>
-    <row r="114" ht="15.75" customHeight="1" s="35"/>
-    <row r="115" ht="15.75" customHeight="1" s="35"/>
-    <row r="116" ht="15.75" customHeight="1" s="35"/>
-    <row r="117" ht="15.75" customHeight="1" s="35"/>
-    <row r="118" ht="15.75" customHeight="1" s="35"/>
-    <row r="119" ht="15.75" customHeight="1" s="35"/>
-    <row r="120" ht="15.75" customHeight="1" s="35"/>
-    <row r="121" ht="15.75" customHeight="1" s="35"/>
-    <row r="122" ht="15.75" customHeight="1" s="35"/>
-    <row r="123" ht="15.75" customHeight="1" s="35"/>
-    <row r="124" ht="15.75" customHeight="1" s="35"/>
-    <row r="125" ht="15.75" customHeight="1" s="35"/>
-    <row r="126" ht="15.75" customHeight="1" s="35"/>
-    <row r="127" ht="15.75" customHeight="1" s="35"/>
-    <row r="128" ht="15.75" customHeight="1" s="35"/>
-    <row r="129" ht="15.75" customHeight="1" s="35"/>
-    <row r="130" ht="15.75" customHeight="1" s="35"/>
-    <row r="131" ht="15.75" customHeight="1" s="35"/>
-    <row r="132" ht="15.75" customHeight="1" s="35"/>
-    <row r="133" ht="15.75" customHeight="1" s="35"/>
-    <row r="134" ht="15.75" customHeight="1" s="35"/>
-    <row r="135" ht="15.75" customHeight="1" s="35"/>
-    <row r="136" ht="15.75" customHeight="1" s="35"/>
-    <row r="137" ht="15.75" customHeight="1" s="35"/>
-    <row r="138" ht="15.75" customHeight="1" s="35"/>
-    <row r="139" ht="15.75" customHeight="1" s="35"/>
-    <row r="140" ht="15.75" customHeight="1" s="35"/>
-    <row r="141" ht="15.75" customHeight="1" s="35"/>
-    <row r="142" ht="15.75" customHeight="1" s="35"/>
-    <row r="143" ht="15.75" customHeight="1" s="35"/>
-    <row r="144" ht="15.75" customHeight="1" s="35"/>
-    <row r="145" ht="15.75" customHeight="1" s="35"/>
-    <row r="146" ht="15.75" customHeight="1" s="35"/>
-    <row r="147" ht="15.75" customHeight="1" s="35"/>
-    <row r="148" ht="15.75" customHeight="1" s="35"/>
-    <row r="149" ht="15.75" customHeight="1" s="35"/>
-    <row r="150" ht="15.75" customHeight="1" s="35"/>
-    <row r="151" ht="15.75" customHeight="1" s="35"/>
-    <row r="152" ht="15.75" customHeight="1" s="35"/>
-    <row r="153" ht="15.75" customHeight="1" s="35"/>
-    <row r="154" ht="15.75" customHeight="1" s="35"/>
-    <row r="155" ht="15.75" customHeight="1" s="35"/>
-    <row r="156" ht="15.75" customHeight="1" s="35"/>
-    <row r="157" ht="15.75" customHeight="1" s="35"/>
-    <row r="158" ht="15.75" customHeight="1" s="35"/>
-    <row r="159" ht="15.75" customHeight="1" s="35"/>
-    <row r="160" ht="15.75" customHeight="1" s="35"/>
-    <row r="161" ht="15.75" customHeight="1" s="35"/>
-    <row r="162" ht="15.75" customHeight="1" s="35"/>
-    <row r="163" ht="15.75" customHeight="1" s="35"/>
-    <row r="164" ht="15.75" customHeight="1" s="35"/>
-    <row r="165" ht="15.75" customHeight="1" s="35"/>
-    <row r="166" ht="15.75" customHeight="1" s="35"/>
-    <row r="167" ht="15.75" customHeight="1" s="35"/>
-    <row r="168" ht="15.75" customHeight="1" s="35"/>
-    <row r="169" ht="15.75" customHeight="1" s="35"/>
-    <row r="170" ht="15.75" customHeight="1" s="35"/>
-    <row r="171" ht="15.75" customHeight="1" s="35"/>
-    <row r="172" ht="15.75" customHeight="1" s="35"/>
-    <row r="173" ht="15.75" customHeight="1" s="35"/>
-    <row r="174" ht="15.75" customHeight="1" s="35"/>
-    <row r="175" ht="15.75" customHeight="1" s="35"/>
-    <row r="176" ht="15.75" customHeight="1" s="35"/>
-    <row r="177" ht="15.75" customHeight="1" s="35"/>
-    <row r="178" ht="15.75" customHeight="1" s="35"/>
-    <row r="179" ht="15.75" customHeight="1" s="35"/>
-    <row r="180" ht="15.75" customHeight="1" s="35"/>
-    <row r="181" ht="15.75" customHeight="1" s="35"/>
-    <row r="182" ht="15.75" customHeight="1" s="35"/>
-    <row r="183" ht="15.75" customHeight="1" s="35"/>
-    <row r="184" ht="15.75" customHeight="1" s="35"/>
-    <row r="185" ht="15.75" customHeight="1" s="35"/>
-    <row r="186" ht="15.75" customHeight="1" s="35"/>
-    <row r="187" ht="15.75" customHeight="1" s="35"/>
-    <row r="188" ht="15.75" customHeight="1" s="35"/>
-    <row r="189" ht="15.75" customHeight="1" s="35"/>
-    <row r="190" ht="15.75" customHeight="1" s="35"/>
-    <row r="191" ht="15.75" customHeight="1" s="35"/>
-    <row r="192" ht="15.75" customHeight="1" s="35"/>
-    <row r="193" ht="15.75" customHeight="1" s="35"/>
-    <row r="194" ht="15.75" customHeight="1" s="35"/>
-    <row r="195" ht="15.75" customHeight="1" s="35"/>
-    <row r="196" ht="15.75" customHeight="1" s="35"/>
-    <row r="197" ht="15.75" customHeight="1" s="35"/>
-    <row r="198" ht="15.75" customHeight="1" s="35"/>
-    <row r="199" ht="15.75" customHeight="1" s="35"/>
-    <row r="200" ht="15.75" customHeight="1" s="35"/>
-    <row r="201" ht="15.75" customHeight="1" s="35"/>
-    <row r="202" ht="15.75" customHeight="1" s="35"/>
-    <row r="203" ht="15.75" customHeight="1" s="35"/>
-    <row r="204" ht="15.75" customHeight="1" s="35"/>
-    <row r="205" ht="15.75" customHeight="1" s="35"/>
-    <row r="206" ht="15.75" customHeight="1" s="35"/>
-    <row r="207" ht="15.75" customHeight="1" s="35"/>
-    <row r="208" ht="15.75" customHeight="1" s="35"/>
-    <row r="209" ht="15.75" customHeight="1" s="35"/>
-    <row r="210" ht="15.75" customHeight="1" s="35"/>
-    <row r="211" ht="15.75" customHeight="1" s="35"/>
-    <row r="212" ht="15.75" customHeight="1" s="35"/>
-    <row r="213" ht="15.75" customHeight="1" s="35"/>
-    <row r="214" ht="15.75" customHeight="1" s="35"/>
-    <row r="215" ht="15.75" customHeight="1" s="35"/>
-    <row r="216" ht="15.75" customHeight="1" s="35"/>
-    <row r="217" ht="15.75" customHeight="1" s="35"/>
-    <row r="218" ht="15.75" customHeight="1" s="35"/>
-    <row r="219" ht="15.75" customHeight="1" s="35"/>
-    <row r="220" ht="15.75" customHeight="1" s="35"/>
-    <row r="221" ht="15.75" customHeight="1" s="35"/>
-    <row r="222" ht="15.75" customHeight="1" s="35"/>
-    <row r="223" ht="15.75" customHeight="1" s="35"/>
-    <row r="224" ht="15.75" customHeight="1" s="35"/>
-    <row r="225" ht="15.75" customHeight="1" s="35"/>
-    <row r="226" ht="15.75" customHeight="1" s="35"/>
-    <row r="227" ht="15.75" customHeight="1" s="35"/>
-    <row r="228" ht="15.75" customHeight="1" s="35"/>
-    <row r="229" ht="15.75" customHeight="1" s="35"/>
-    <row r="230" ht="15.75" customHeight="1" s="35"/>
-    <row r="231" ht="15.75" customHeight="1" s="35"/>
-    <row r="232" ht="15.75" customHeight="1" s="35"/>
-    <row r="233" ht="15.75" customHeight="1" s="35"/>
-    <row r="234" ht="15.75" customHeight="1" s="35"/>
-    <row r="235" ht="15.75" customHeight="1" s="35"/>
-    <row r="236" ht="15.75" customHeight="1" s="35"/>
-    <row r="237" ht="15.75" customHeight="1" s="35"/>
-    <row r="238" ht="15.75" customHeight="1" s="35"/>
-    <row r="239" ht="15.75" customHeight="1" s="35"/>
-    <row r="240" ht="15.75" customHeight="1" s="35"/>
-    <row r="241" ht="15.75" customHeight="1" s="35"/>
-    <row r="242" ht="15.75" customHeight="1" s="35"/>
-    <row r="243" ht="15.75" customHeight="1" s="35"/>
-    <row r="244" ht="15.75" customHeight="1" s="35"/>
-    <row r="245" ht="15.75" customHeight="1" s="35"/>
-    <row r="246" ht="15.75" customHeight="1" s="35"/>
-    <row r="247" ht="15.75" customHeight="1" s="35"/>
-    <row r="248" ht="15.75" customHeight="1" s="35"/>
-    <row r="249" ht="15.75" customHeight="1" s="35"/>
-    <row r="250" ht="15.75" customHeight="1" s="35"/>
-    <row r="251" ht="15.75" customHeight="1" s="35"/>
-    <row r="252" ht="15.75" customHeight="1" s="35"/>
-    <row r="253" ht="15.75" customHeight="1" s="35"/>
-    <row r="254" ht="15.75" customHeight="1" s="35"/>
-    <row r="255" ht="15.75" customHeight="1" s="35"/>
-    <row r="256" ht="15.75" customHeight="1" s="35"/>
-    <row r="257" ht="15.75" customHeight="1" s="35"/>
-    <row r="258" ht="15.75" customHeight="1" s="35"/>
-    <row r="259" ht="15.75" customHeight="1" s="35"/>
-    <row r="260" ht="15.75" customHeight="1" s="35"/>
-    <row r="261" ht="15.75" customHeight="1" s="35"/>
-    <row r="262" ht="15.75" customHeight="1" s="35"/>
-    <row r="263" ht="15.75" customHeight="1" s="35"/>
-    <row r="264" ht="15.75" customHeight="1" s="35"/>
-    <row r="265" ht="15.75" customHeight="1" s="35"/>
-    <row r="266" ht="15.75" customHeight="1" s="35"/>
-    <row r="267" ht="15.75" customHeight="1" s="35"/>
-    <row r="268" ht="15.75" customHeight="1" s="35"/>
-    <row r="269" ht="15.75" customHeight="1" s="35"/>
-    <row r="270" ht="15.75" customHeight="1" s="35"/>
-    <row r="271" ht="15.75" customHeight="1" s="35"/>
-    <row r="272" ht="15.75" customHeight="1" s="35"/>
-    <row r="273" ht="15.75" customHeight="1" s="35"/>
-    <row r="274" ht="15.75" customHeight="1" s="35"/>
-    <row r="275" ht="15.75" customHeight="1" s="35"/>
-    <row r="276" ht="15.75" customHeight="1" s="35"/>
-    <row r="277" ht="15.75" customHeight="1" s="35"/>
-    <row r="278" ht="15.75" customHeight="1" s="35"/>
-    <row r="279" ht="15.75" customHeight="1" s="35"/>
-    <row r="280" ht="15.75" customHeight="1" s="35"/>
-    <row r="281" ht="15.75" customHeight="1" s="35"/>
-    <row r="282" ht="15.75" customHeight="1" s="35"/>
-    <row r="283" ht="15.75" customHeight="1" s="35"/>
-    <row r="284" ht="15.75" customHeight="1" s="35"/>
-    <row r="285" ht="15.75" customHeight="1" s="35"/>
-    <row r="286" ht="15.75" customHeight="1" s="35"/>
-    <row r="287" ht="15.75" customHeight="1" s="35"/>
-    <row r="288" ht="15.75" customHeight="1" s="35"/>
-    <row r="289" ht="15.75" customHeight="1" s="35"/>
-    <row r="290" ht="15.75" customHeight="1" s="35"/>
-    <row r="291" ht="15.75" customHeight="1" s="35"/>
-    <row r="292" ht="15.75" customHeight="1" s="35"/>
-    <row r="293" ht="15.75" customHeight="1" s="35"/>
-    <row r="294" ht="15.75" customHeight="1" s="35"/>
-    <row r="295" ht="15.75" customHeight="1" s="35"/>
-    <row r="296" ht="15.75" customHeight="1" s="35"/>
-    <row r="297" ht="15.75" customHeight="1" s="35"/>
-    <row r="298" ht="15.75" customHeight="1" s="35"/>
-    <row r="299" ht="15.75" customHeight="1" s="35"/>
-    <row r="300" ht="15.75" customHeight="1" s="35"/>
-    <row r="301" ht="15.75" customHeight="1" s="35"/>
-    <row r="302" ht="15.75" customHeight="1" s="35"/>
-    <row r="303" ht="15.75" customHeight="1" s="35"/>
-    <row r="304" ht="15.75" customHeight="1" s="35"/>
-    <row r="305" ht="15.75" customHeight="1" s="35"/>
-    <row r="306" ht="15.75" customHeight="1" s="35"/>
-    <row r="307" ht="15.75" customHeight="1" s="35"/>
-    <row r="308" ht="15.75" customHeight="1" s="35"/>
-    <row r="309" ht="15.75" customHeight="1" s="35"/>
-    <row r="310" ht="15.75" customHeight="1" s="35"/>
-    <row r="311" ht="15.75" customHeight="1" s="35"/>
-    <row r="312" ht="15.75" customHeight="1" s="35"/>
-    <row r="313" ht="15.75" customHeight="1" s="35"/>
-    <row r="314" ht="15.75" customHeight="1" s="35"/>
-    <row r="315" ht="15.75" customHeight="1" s="35"/>
-    <row r="316" ht="15.75" customHeight="1" s="35"/>
-    <row r="317" ht="15.75" customHeight="1" s="35"/>
-    <row r="318" ht="15.75" customHeight="1" s="35"/>
-    <row r="319" ht="15.75" customHeight="1" s="35"/>
-    <row r="320" ht="15.75" customHeight="1" s="35"/>
-    <row r="321" ht="15.75" customHeight="1" s="35"/>
-    <row r="322" ht="15.75" customHeight="1" s="35"/>
-    <row r="323" ht="15.75" customHeight="1" s="35"/>
-    <row r="324" ht="15.75" customHeight="1" s="35"/>
-    <row r="325" ht="15.75" customHeight="1" s="35"/>
-    <row r="326" ht="15.75" customHeight="1" s="35"/>
-    <row r="327" ht="15.75" customHeight="1" s="35"/>
-    <row r="328" ht="15.75" customHeight="1" s="35"/>
-    <row r="329" ht="15.75" customHeight="1" s="35"/>
-    <row r="330" ht="15.75" customHeight="1" s="35"/>
-    <row r="331" ht="15.75" customHeight="1" s="35"/>
-    <row r="332" ht="15.75" customHeight="1" s="35"/>
-    <row r="333" ht="15.75" customHeight="1" s="35"/>
-    <row r="334" ht="15.75" customHeight="1" s="35"/>
-    <row r="335" ht="15.75" customHeight="1" s="35"/>
-    <row r="336" ht="15.75" customHeight="1" s="35"/>
-    <row r="337" ht="15.75" customHeight="1" s="35"/>
-    <row r="338" ht="15.75" customHeight="1" s="35"/>
-    <row r="339" ht="15.75" customHeight="1" s="35"/>
-    <row r="340" ht="15.75" customHeight="1" s="35"/>
-    <row r="341" ht="15.75" customHeight="1" s="35"/>
-    <row r="342" ht="15.75" customHeight="1" s="35"/>
-    <row r="343" ht="15.75" customHeight="1" s="35"/>
-    <row r="344" ht="15.75" customHeight="1" s="35"/>
-    <row r="345" ht="15.75" customHeight="1" s="35"/>
-    <row r="346" ht="15.75" customHeight="1" s="35"/>
-    <row r="347" ht="15.75" customHeight="1" s="35"/>
-    <row r="348" ht="15.75" customHeight="1" s="35"/>
-    <row r="349" ht="15.75" customHeight="1" s="35"/>
-    <row r="350" ht="15.75" customHeight="1" s="35"/>
-    <row r="351" ht="15.75" customHeight="1" s="35"/>
-    <row r="352" ht="15.75" customHeight="1" s="35"/>
-    <row r="353" ht="15.75" customHeight="1" s="35"/>
-    <row r="354" ht="15.75" customHeight="1" s="35"/>
-    <row r="355" ht="15.75" customHeight="1" s="35"/>
-    <row r="356" ht="15.75" customHeight="1" s="35"/>
-    <row r="357" ht="15.75" customHeight="1" s="35"/>
-    <row r="358" ht="15.75" customHeight="1" s="35"/>
-    <row r="359" ht="15.75" customHeight="1" s="35"/>
-    <row r="360" ht="15.75" customHeight="1" s="35"/>
-    <row r="361" ht="15.75" customHeight="1" s="35"/>
-    <row r="362" ht="15.75" customHeight="1" s="35"/>
-    <row r="363" ht="15.75" customHeight="1" s="35"/>
-    <row r="364" ht="15.75" customHeight="1" s="35"/>
-    <row r="365" ht="15.75" customHeight="1" s="35"/>
-    <row r="366" ht="15.75" customHeight="1" s="35"/>
-    <row r="367" ht="15.75" customHeight="1" s="35"/>
-    <row r="368" ht="15.75" customHeight="1" s="35"/>
-    <row r="369" ht="15.75" customHeight="1" s="35"/>
-    <row r="370" ht="15.75" customHeight="1" s="35"/>
-    <row r="371" ht="15.75" customHeight="1" s="35"/>
-    <row r="372" ht="15.75" customHeight="1" s="35"/>
-    <row r="373" ht="15.75" customHeight="1" s="35"/>
-    <row r="374" ht="15.75" customHeight="1" s="35"/>
-    <row r="375" ht="15.75" customHeight="1" s="35"/>
-    <row r="376" ht="15.75" customHeight="1" s="35"/>
-    <row r="377" ht="15.75" customHeight="1" s="35"/>
-    <row r="378" ht="15.75" customHeight="1" s="35"/>
-    <row r="379" ht="15.75" customHeight="1" s="35"/>
-    <row r="380" ht="15.75" customHeight="1" s="35"/>
-    <row r="381" ht="15.75" customHeight="1" s="35"/>
-    <row r="382" ht="15.75" customHeight="1" s="35"/>
-    <row r="383" ht="15.75" customHeight="1" s="35"/>
-    <row r="384" ht="15.75" customHeight="1" s="35"/>
-    <row r="385" ht="15.75" customHeight="1" s="35"/>
-    <row r="386" ht="15.75" customHeight="1" s="35"/>
-    <row r="387" ht="15.75" customHeight="1" s="35"/>
-    <row r="388" ht="15.75" customHeight="1" s="35"/>
-    <row r="389" ht="15.75" customHeight="1" s="35"/>
-    <row r="390" ht="15.75" customHeight="1" s="35"/>
-    <row r="391" ht="15.75" customHeight="1" s="35"/>
-    <row r="392" ht="15.75" customHeight="1" s="35"/>
-    <row r="393" ht="15.75" customHeight="1" s="35"/>
-    <row r="394" ht="15.75" customHeight="1" s="35"/>
-    <row r="395" ht="15.75" customHeight="1" s="35"/>
-    <row r="396" ht="15.75" customHeight="1" s="35"/>
-    <row r="397" ht="15.75" customHeight="1" s="35"/>
-    <row r="398" ht="15.75" customHeight="1" s="35"/>
-    <row r="399" ht="15.75" customHeight="1" s="35"/>
-    <row r="400" ht="15.75" customHeight="1" s="35"/>
-    <row r="401" ht="15.75" customHeight="1" s="35"/>
-    <row r="402" ht="15.75" customHeight="1" s="35"/>
-    <row r="403" ht="15.75" customHeight="1" s="35"/>
-    <row r="404" ht="15.75" customHeight="1" s="35"/>
-    <row r="405" ht="15.75" customHeight="1" s="35"/>
-    <row r="406" ht="15.75" customHeight="1" s="35"/>
-    <row r="407" ht="15.75" customHeight="1" s="35"/>
-    <row r="408" ht="15.75" customHeight="1" s="35"/>
-    <row r="409" ht="15.75" customHeight="1" s="35"/>
-    <row r="410" ht="15.75" customHeight="1" s="35"/>
-    <row r="411" ht="15.75" customHeight="1" s="35"/>
-    <row r="412" ht="15.75" customHeight="1" s="35"/>
-    <row r="413" ht="15.75" customHeight="1" s="35"/>
-    <row r="414" ht="15.75" customHeight="1" s="35"/>
-    <row r="415" ht="15.75" customHeight="1" s="35"/>
-    <row r="416" ht="15.75" customHeight="1" s="35"/>
-    <row r="417" ht="15.75" customHeight="1" s="35"/>
-    <row r="418" ht="15.75" customHeight="1" s="35"/>
-    <row r="419" ht="15.75" customHeight="1" s="35"/>
-    <row r="420" ht="15.75" customHeight="1" s="35"/>
-    <row r="421" ht="15.75" customHeight="1" s="35"/>
-    <row r="422" ht="15.75" customHeight="1" s="35"/>
-    <row r="423" ht="15.75" customHeight="1" s="35"/>
-    <row r="424" ht="15.75" customHeight="1" s="35"/>
-    <row r="425" ht="15.75" customHeight="1" s="35"/>
-    <row r="426" ht="15.75" customHeight="1" s="35"/>
-    <row r="427" ht="15.75" customHeight="1" s="35"/>
-    <row r="428" ht="15.75" customHeight="1" s="35"/>
-    <row r="429" ht="15.75" customHeight="1" s="35"/>
-    <row r="430" ht="15.75" customHeight="1" s="35"/>
-    <row r="431" ht="15.75" customHeight="1" s="35"/>
-    <row r="432" ht="15.75" customHeight="1" s="35"/>
-    <row r="433" ht="15.75" customHeight="1" s="35"/>
-    <row r="434" ht="15.75" customHeight="1" s="35"/>
-    <row r="435" ht="15.75" customHeight="1" s="35"/>
-    <row r="436" ht="15.75" customHeight="1" s="35"/>
-    <row r="437" ht="15.75" customHeight="1" s="35"/>
-    <row r="438" ht="15.75" customHeight="1" s="35"/>
-    <row r="439" ht="15.75" customHeight="1" s="35"/>
-    <row r="440" ht="15.75" customHeight="1" s="35"/>
-    <row r="441" ht="15.75" customHeight="1" s="35"/>
-    <row r="442" ht="15.75" customHeight="1" s="35"/>
-    <row r="443" ht="15.75" customHeight="1" s="35"/>
-    <row r="444" ht="15.75" customHeight="1" s="35"/>
-    <row r="445" ht="15.75" customHeight="1" s="35"/>
-    <row r="446" ht="15.75" customHeight="1" s="35"/>
-    <row r="447" ht="15.75" customHeight="1" s="35"/>
-    <row r="448" ht="15.75" customHeight="1" s="35"/>
-    <row r="449" ht="15.75" customHeight="1" s="35"/>
-    <row r="450" ht="15.75" customHeight="1" s="35"/>
-    <row r="451" ht="15.75" customHeight="1" s="35"/>
-    <row r="452" ht="15.75" customHeight="1" s="35"/>
-    <row r="453" ht="15.75" customHeight="1" s="35"/>
-    <row r="454" ht="15.75" customHeight="1" s="35"/>
-    <row r="455" ht="15.75" customHeight="1" s="35"/>
-    <row r="456" ht="15.75" customHeight="1" s="35"/>
-    <row r="457" ht="15.75" customHeight="1" s="35"/>
-    <row r="458" ht="15.75" customHeight="1" s="35"/>
-    <row r="459" ht="15.75" customHeight="1" s="35"/>
-    <row r="460" ht="15.75" customHeight="1" s="35"/>
-    <row r="461" ht="15.75" customHeight="1" s="35"/>
-    <row r="462" ht="15.75" customHeight="1" s="35"/>
-    <row r="463" ht="15.75" customHeight="1" s="35"/>
-    <row r="464" ht="15.75" customHeight="1" s="35"/>
-    <row r="465" ht="15.75" customHeight="1" s="35"/>
-    <row r="466" ht="15.75" customHeight="1" s="35"/>
-    <row r="467" ht="15.75" customHeight="1" s="35"/>
-    <row r="468" ht="15.75" customHeight="1" s="35"/>
-    <row r="469" ht="15.75" customHeight="1" s="35"/>
-    <row r="470" ht="15.75" customHeight="1" s="35"/>
-    <row r="471" ht="15.75" customHeight="1" s="35"/>
-    <row r="472" ht="15.75" customHeight="1" s="35"/>
-    <row r="473" ht="15.75" customHeight="1" s="35"/>
-    <row r="474" ht="15.75" customHeight="1" s="35"/>
-    <row r="475" ht="15.75" customHeight="1" s="35"/>
-    <row r="476" ht="15.75" customHeight="1" s="35"/>
-    <row r="477" ht="15.75" customHeight="1" s="35"/>
-    <row r="478" ht="15.75" customHeight="1" s="35"/>
-    <row r="479" ht="15.75" customHeight="1" s="35"/>
-    <row r="480" ht="15.75" customHeight="1" s="35"/>
-    <row r="481" ht="15.75" customHeight="1" s="35"/>
-    <row r="482" ht="15.75" customHeight="1" s="35"/>
-    <row r="483" ht="15.75" customHeight="1" s="35"/>
-    <row r="484" ht="15.75" customHeight="1" s="35"/>
-    <row r="485" ht="15.75" customHeight="1" s="35"/>
-    <row r="486" ht="15.75" customHeight="1" s="35"/>
-    <row r="487" ht="15.75" customHeight="1" s="35"/>
-    <row r="488" ht="15.75" customHeight="1" s="35"/>
-    <row r="489" ht="15.75" customHeight="1" s="35"/>
-    <row r="490" ht="15.75" customHeight="1" s="35"/>
-    <row r="491" ht="15.75" customHeight="1" s="35"/>
-    <row r="492" ht="15.75" customHeight="1" s="35"/>
-    <row r="493" ht="15.75" customHeight="1" s="35"/>
-    <row r="494" ht="15.75" customHeight="1" s="35"/>
-    <row r="495" ht="15.75" customHeight="1" s="35"/>
-    <row r="496" ht="15.75" customHeight="1" s="35"/>
-    <row r="497" ht="15.75" customHeight="1" s="35"/>
-    <row r="498" ht="15.75" customHeight="1" s="35"/>
-    <row r="499" ht="15.75" customHeight="1" s="35"/>
-    <row r="500" ht="15.75" customHeight="1" s="35"/>
-    <row r="501" ht="15.75" customHeight="1" s="35"/>
-    <row r="502" ht="15.75" customHeight="1" s="35"/>
-    <row r="503" ht="15.75" customHeight="1" s="35"/>
-    <row r="504" ht="15.75" customHeight="1" s="35"/>
-    <row r="505" ht="15.75" customHeight="1" s="35"/>
-    <row r="506" ht="15.75" customHeight="1" s="35"/>
-    <row r="507" ht="15.75" customHeight="1" s="35"/>
-    <row r="508" ht="15.75" customHeight="1" s="35"/>
-    <row r="509" ht="15.75" customHeight="1" s="35"/>
-    <row r="510" ht="15.75" customHeight="1" s="35"/>
-    <row r="511" ht="15.75" customHeight="1" s="35"/>
-    <row r="512" ht="15.75" customHeight="1" s="35"/>
-    <row r="513" ht="15.75" customHeight="1" s="35"/>
-    <row r="514" ht="15.75" customHeight="1" s="35"/>
-    <row r="515" ht="15.75" customHeight="1" s="35"/>
-    <row r="516" ht="15.75" customHeight="1" s="35"/>
-    <row r="517" ht="15.75" customHeight="1" s="35"/>
-    <row r="518" ht="15.75" customHeight="1" s="35"/>
-    <row r="519" ht="15.75" customHeight="1" s="35"/>
-    <row r="520" ht="15.75" customHeight="1" s="35"/>
-    <row r="521" ht="15.75" customHeight="1" s="35"/>
-    <row r="522" ht="15.75" customHeight="1" s="35"/>
-    <row r="523" ht="15.75" customHeight="1" s="35"/>
-    <row r="524" ht="15.75" customHeight="1" s="35"/>
-    <row r="525" ht="15.75" customHeight="1" s="35"/>
-    <row r="526" ht="15.75" customHeight="1" s="35"/>
-    <row r="527" ht="15.75" customHeight="1" s="35"/>
-    <row r="528" ht="15.75" customHeight="1" s="35"/>
-    <row r="529" ht="15.75" customHeight="1" s="35"/>
-    <row r="530" ht="15.75" customHeight="1" s="35"/>
-    <row r="531" ht="15.75" customHeight="1" s="35"/>
-    <row r="532" ht="15.75" customHeight="1" s="35"/>
-    <row r="533" ht="15.75" customHeight="1" s="35"/>
-    <row r="534" ht="15.75" customHeight="1" s="35"/>
-    <row r="535" ht="15.75" customHeight="1" s="35"/>
-    <row r="536" ht="15.75" customHeight="1" s="35"/>
-    <row r="537" ht="15.75" customHeight="1" s="35"/>
-    <row r="538" ht="15.75" customHeight="1" s="35"/>
-    <row r="539" ht="15.75" customHeight="1" s="35"/>
-    <row r="540" ht="15.75" customHeight="1" s="35"/>
-    <row r="541" ht="15.75" customHeight="1" s="35"/>
-    <row r="542" ht="15.75" customHeight="1" s="35"/>
-    <row r="543" ht="15.75" customHeight="1" s="35"/>
-    <row r="544" ht="15.75" customHeight="1" s="35"/>
-    <row r="545" ht="15.75" customHeight="1" s="35"/>
-    <row r="546" ht="15.75" customHeight="1" s="35"/>
-    <row r="547" ht="15.75" customHeight="1" s="35"/>
-    <row r="548" ht="15.75" customHeight="1" s="35"/>
-    <row r="549" ht="15.75" customHeight="1" s="35"/>
-    <row r="550" ht="15.75" customHeight="1" s="35"/>
-    <row r="551" ht="15.75" customHeight="1" s="35"/>
-    <row r="552" ht="15.75" customHeight="1" s="35"/>
-    <row r="553" ht="15.75" customHeight="1" s="35"/>
-    <row r="554" ht="15.75" customHeight="1" s="35"/>
-    <row r="555" ht="15.75" customHeight="1" s="35"/>
-    <row r="556" ht="15.75" customHeight="1" s="35"/>
-    <row r="557" ht="15.75" customHeight="1" s="35"/>
-    <row r="558" ht="15.75" customHeight="1" s="35"/>
-    <row r="559" ht="15.75" customHeight="1" s="35"/>
-    <row r="560" ht="15.75" customHeight="1" s="35"/>
-    <row r="561" ht="15.75" customHeight="1" s="35"/>
-    <row r="562" ht="15.75" customHeight="1" s="35"/>
-    <row r="563" ht="15.75" customHeight="1" s="35"/>
-    <row r="564" ht="15.75" customHeight="1" s="35"/>
-    <row r="565" ht="15.75" customHeight="1" s="35"/>
-    <row r="566" ht="15.75" customHeight="1" s="35"/>
-    <row r="567" ht="15.75" customHeight="1" s="35"/>
-    <row r="568" ht="15.75" customHeight="1" s="35"/>
-    <row r="569" ht="15.75" customHeight="1" s="35"/>
-    <row r="570" ht="15.75" customHeight="1" s="35"/>
-    <row r="571" ht="15.75" customHeight="1" s="35"/>
-    <row r="572" ht="15.75" customHeight="1" s="35"/>
-    <row r="573" ht="15.75" customHeight="1" s="35"/>
-    <row r="574" ht="15.75" customHeight="1" s="35"/>
-    <row r="575" ht="15.75" customHeight="1" s="35"/>
-    <row r="576" ht="15.75" customHeight="1" s="35"/>
-    <row r="577" ht="15.75" customHeight="1" s="35"/>
-    <row r="578" ht="15.75" customHeight="1" s="35"/>
-    <row r="579" ht="15.75" customHeight="1" s="35"/>
-    <row r="580" ht="15.75" customHeight="1" s="35"/>
-    <row r="581" ht="15.75" customHeight="1" s="35"/>
-    <row r="582" ht="15.75" customHeight="1" s="35"/>
-    <row r="583" ht="15.75" customHeight="1" s="35"/>
-    <row r="584" ht="15.75" customHeight="1" s="35"/>
-    <row r="585" ht="15.75" customHeight="1" s="35"/>
-    <row r="586" ht="15.75" customHeight="1" s="35"/>
-    <row r="587" ht="15.75" customHeight="1" s="35"/>
-    <row r="588" ht="15.75" customHeight="1" s="35"/>
-    <row r="589" ht="15.75" customHeight="1" s="35"/>
-    <row r="590" ht="15.75" customHeight="1" s="35"/>
-    <row r="591" ht="15.75" customHeight="1" s="35"/>
-    <row r="592" ht="15.75" customHeight="1" s="35"/>
-    <row r="593" ht="15.75" customHeight="1" s="35"/>
-    <row r="594" ht="15.75" customHeight="1" s="35"/>
-    <row r="595" ht="15.75" customHeight="1" s="35"/>
-    <row r="596" ht="15.75" customHeight="1" s="35"/>
-    <row r="597" ht="15.75" customHeight="1" s="35"/>
-    <row r="598" ht="15.75" customHeight="1" s="35"/>
-    <row r="599" ht="15.75" customHeight="1" s="35"/>
-    <row r="600" ht="15.75" customHeight="1" s="35"/>
-    <row r="601" ht="15.75" customHeight="1" s="35"/>
-    <row r="602" ht="15.75" customHeight="1" s="35"/>
-    <row r="603" ht="15.75" customHeight="1" s="35"/>
-    <row r="604" ht="15.75" customHeight="1" s="35"/>
-    <row r="605" ht="15.75" customHeight="1" s="35"/>
-    <row r="606" ht="15.75" customHeight="1" s="35"/>
-    <row r="607" ht="15.75" customHeight="1" s="35"/>
-    <row r="608" ht="15.75" customHeight="1" s="35"/>
-    <row r="609" ht="15.75" customHeight="1" s="35"/>
-    <row r="610" ht="15.75" customHeight="1" s="35"/>
-    <row r="611" ht="15.75" customHeight="1" s="35"/>
-    <row r="612" ht="15.75" customHeight="1" s="35"/>
-    <row r="613" ht="15.75" customHeight="1" s="35"/>
-    <row r="614" ht="15.75" customHeight="1" s="35"/>
-    <row r="615" ht="15.75" customHeight="1" s="35"/>
-    <row r="616" ht="15.75" customHeight="1" s="35"/>
-    <row r="617" ht="15.75" customHeight="1" s="35"/>
-    <row r="618" ht="15.75" customHeight="1" s="35"/>
-    <row r="619" ht="15.75" customHeight="1" s="35"/>
-    <row r="620" ht="15.75" customHeight="1" s="35"/>
-    <row r="621" ht="15.75" customHeight="1" s="35"/>
-    <row r="622" ht="15.75" customHeight="1" s="35"/>
-    <row r="623" ht="15.75" customHeight="1" s="35"/>
-    <row r="624" ht="15.75" customHeight="1" s="35"/>
-    <row r="625" ht="15.75" customHeight="1" s="35"/>
-    <row r="626" ht="15.75" customHeight="1" s="35"/>
-    <row r="627" ht="15.75" customHeight="1" s="35"/>
-    <row r="628" ht="15.75" customHeight="1" s="35"/>
-    <row r="629" ht="15.75" customHeight="1" s="35"/>
-    <row r="630" ht="15.75" customHeight="1" s="35"/>
-    <row r="631" ht="15.75" customHeight="1" s="35"/>
-    <row r="632" ht="15.75" customHeight="1" s="35"/>
-    <row r="633" ht="15.75" customHeight="1" s="35"/>
-    <row r="634" ht="15.75" customHeight="1" s="35"/>
-    <row r="635" ht="15.75" customHeight="1" s="35"/>
-    <row r="636" ht="15.75" customHeight="1" s="35"/>
-    <row r="637" ht="15.75" customHeight="1" s="35"/>
-    <row r="638" ht="15.75" customHeight="1" s="35"/>
-    <row r="639" ht="15.75" customHeight="1" s="35"/>
-    <row r="640" ht="15.75" customHeight="1" s="35"/>
-    <row r="641" ht="15.75" customHeight="1" s="35"/>
-    <row r="642" ht="15.75" customHeight="1" s="35"/>
-    <row r="643" ht="15.75" customHeight="1" s="35"/>
-    <row r="644" ht="15.75" customHeight="1" s="35"/>
-    <row r="645" ht="15.75" customHeight="1" s="35"/>
-    <row r="646" ht="15.75" customHeight="1" s="35"/>
-    <row r="647" ht="15.75" customHeight="1" s="35"/>
-    <row r="648" ht="15.75" customHeight="1" s="35"/>
-    <row r="649" ht="15.75" customHeight="1" s="35"/>
-    <row r="650" ht="15.75" customHeight="1" s="35"/>
-    <row r="651" ht="15.75" customHeight="1" s="35"/>
-    <row r="652" ht="15.75" customHeight="1" s="35"/>
-    <row r="653" ht="15.75" customHeight="1" s="35"/>
-    <row r="654" ht="15.75" customHeight="1" s="35"/>
-    <row r="655" ht="15.75" customHeight="1" s="35"/>
-    <row r="656" ht="15.75" customHeight="1" s="35"/>
-    <row r="657" ht="15.75" customHeight="1" s="35"/>
-    <row r="658" ht="15.75" customHeight="1" s="35"/>
-    <row r="659" ht="15.75" customHeight="1" s="35"/>
-    <row r="660" ht="15.75" customHeight="1" s="35"/>
-    <row r="661" ht="15.75" customHeight="1" s="35"/>
-    <row r="662" ht="15.75" customHeight="1" s="35"/>
-    <row r="663" ht="15.75" customHeight="1" s="35"/>
-    <row r="664" ht="15.75" customHeight="1" s="35"/>
-    <row r="665" ht="15.75" customHeight="1" s="35"/>
-    <row r="666" ht="15.75" customHeight="1" s="35"/>
-    <row r="667" ht="15.75" customHeight="1" s="35"/>
-    <row r="668" ht="15.75" customHeight="1" s="35"/>
-    <row r="669" ht="15.75" customHeight="1" s="35"/>
-    <row r="670" ht="15.75" customHeight="1" s="35"/>
-    <row r="671" ht="15.75" customHeight="1" s="35"/>
-    <row r="672" ht="15.75" customHeight="1" s="35"/>
-    <row r="673" ht="15.75" customHeight="1" s="35"/>
-    <row r="674" ht="15.75" customHeight="1" s="35"/>
-    <row r="675" ht="15.75" customHeight="1" s="35"/>
-    <row r="676" ht="15.75" customHeight="1" s="35"/>
-    <row r="677" ht="15.75" customHeight="1" s="35"/>
-    <row r="678" ht="15.75" customHeight="1" s="35"/>
-    <row r="679" ht="15.75" customHeight="1" s="35"/>
-    <row r="680" ht="15.75" customHeight="1" s="35"/>
-    <row r="681" ht="15.75" customHeight="1" s="35"/>
-    <row r="682" ht="15.75" customHeight="1" s="35"/>
-    <row r="683" ht="15.75" customHeight="1" s="35"/>
-    <row r="684" ht="15.75" customHeight="1" s="35"/>
-    <row r="685" ht="15.75" customHeight="1" s="35"/>
-    <row r="686" ht="15.75" customHeight="1" s="35"/>
-    <row r="687" ht="15.75" customHeight="1" s="35"/>
-    <row r="688" ht="15.75" customHeight="1" s="35"/>
-    <row r="689" ht="15.75" customHeight="1" s="35"/>
-    <row r="690" ht="15.75" customHeight="1" s="35"/>
-    <row r="691" ht="15.75" customHeight="1" s="35"/>
-    <row r="692" ht="15.75" customHeight="1" s="35"/>
-    <row r="693" ht="15.75" customHeight="1" s="35"/>
-    <row r="694" ht="15.75" customHeight="1" s="35"/>
-    <row r="695" ht="15.75" customHeight="1" s="35"/>
-    <row r="696" ht="15.75" customHeight="1" s="35"/>
-    <row r="697" ht="15.75" customHeight="1" s="35"/>
-    <row r="698" ht="15.75" customHeight="1" s="35"/>
-    <row r="699" ht="15.75" customHeight="1" s="35"/>
-    <row r="700" ht="15.75" customHeight="1" s="35"/>
-    <row r="701" ht="15.75" customHeight="1" s="35"/>
-    <row r="702" ht="15.75" customHeight="1" s="35"/>
-    <row r="703" ht="15.75" customHeight="1" s="35"/>
-    <row r="704" ht="15.75" customHeight="1" s="35"/>
-    <row r="705" ht="15.75" customHeight="1" s="35"/>
-    <row r="706" ht="15.75" customHeight="1" s="35"/>
-    <row r="707" ht="15.75" customHeight="1" s="35"/>
-    <row r="708" ht="15.75" customHeight="1" s="35"/>
-    <row r="709" ht="15.75" customHeight="1" s="35"/>
-    <row r="710" ht="15.75" customHeight="1" s="35"/>
-    <row r="711" ht="15.75" customHeight="1" s="35"/>
-    <row r="712" ht="15.75" customHeight="1" s="35"/>
-    <row r="713" ht="15.75" customHeight="1" s="35"/>
-    <row r="714" ht="15.75" customHeight="1" s="35"/>
-    <row r="715" ht="15.75" customHeight="1" s="35"/>
-    <row r="716" ht="15.75" customHeight="1" s="35"/>
-    <row r="717" ht="15.75" customHeight="1" s="35"/>
-    <row r="718" ht="15.75" customHeight="1" s="35"/>
-    <row r="719" ht="15.75" customHeight="1" s="35"/>
-    <row r="720" ht="15.75" customHeight="1" s="35"/>
-    <row r="721" ht="15.75" customHeight="1" s="35"/>
-    <row r="722" ht="15.75" customHeight="1" s="35"/>
-    <row r="723" ht="15.75" customHeight="1" s="35"/>
-    <row r="724" ht="15.75" customHeight="1" s="35"/>
-    <row r="725" ht="15.75" customHeight="1" s="35"/>
-    <row r="726" ht="15.75" customHeight="1" s="35"/>
-    <row r="727" ht="15.75" customHeight="1" s="35"/>
-    <row r="728" ht="15.75" customHeight="1" s="35"/>
-    <row r="729" ht="15.75" customHeight="1" s="35"/>
-    <row r="730" ht="15.75" customHeight="1" s="35"/>
-    <row r="731" ht="15.75" customHeight="1" s="35"/>
-    <row r="732" ht="15.75" customHeight="1" s="35"/>
-    <row r="733" ht="15.75" customHeight="1" s="35"/>
-    <row r="734" ht="15.75" customHeight="1" s="35"/>
-    <row r="735" ht="15.75" customHeight="1" s="35"/>
-    <row r="736" ht="15.75" customHeight="1" s="35"/>
-    <row r="737" ht="15.75" customHeight="1" s="35"/>
-    <row r="738" ht="15.75" customHeight="1" s="35"/>
-    <row r="739" ht="15.75" customHeight="1" s="35"/>
-    <row r="740" ht="15.75" customHeight="1" s="35"/>
-    <row r="741" ht="15.75" customHeight="1" s="35"/>
-    <row r="742" ht="15.75" customHeight="1" s="35"/>
-    <row r="743" ht="15.75" customHeight="1" s="35"/>
-    <row r="744" ht="15.75" customHeight="1" s="35"/>
-    <row r="745" ht="15.75" customHeight="1" s="35"/>
-    <row r="746" ht="15.75" customHeight="1" s="35"/>
-    <row r="747" ht="15.75" customHeight="1" s="35"/>
-    <row r="748" ht="15.75" customHeight="1" s="35"/>
-    <row r="749" ht="15.75" customHeight="1" s="35"/>
-    <row r="750" ht="15.75" customHeight="1" s="35"/>
-    <row r="751" ht="15.75" customHeight="1" s="35"/>
-    <row r="752" ht="15.75" customHeight="1" s="35"/>
-    <row r="753" ht="15.75" customHeight="1" s="35"/>
-    <row r="754" ht="15.75" customHeight="1" s="35"/>
-    <row r="755" ht="15.75" customHeight="1" s="35"/>
-    <row r="756" ht="15.75" customHeight="1" s="35"/>
-    <row r="757" ht="15.75" customHeight="1" s="35"/>
-    <row r="758" ht="15.75" customHeight="1" s="35"/>
-    <row r="759" ht="15.75" customHeight="1" s="35"/>
-    <row r="760" ht="15.75" customHeight="1" s="35"/>
-    <row r="761" ht="15.75" customHeight="1" s="35"/>
-    <row r="762" ht="15.75" customHeight="1" s="35"/>
-    <row r="763" ht="15.75" customHeight="1" s="35"/>
-    <row r="764" ht="15.75" customHeight="1" s="35"/>
-    <row r="765" ht="15.75" customHeight="1" s="35"/>
-    <row r="766" ht="15.75" customHeight="1" s="35"/>
-    <row r="767" ht="15.75" customHeight="1" s="35"/>
-    <row r="768" ht="15.75" customHeight="1" s="35"/>
-    <row r="769" ht="15.75" customHeight="1" s="35"/>
-    <row r="770" ht="15.75" customHeight="1" s="35"/>
-    <row r="771" ht="15.75" customHeight="1" s="35"/>
-    <row r="772" ht="15.75" customHeight="1" s="35"/>
-    <row r="773" ht="15.75" customHeight="1" s="35"/>
-    <row r="774" ht="15.75" customHeight="1" s="35"/>
-    <row r="775" ht="15.75" customHeight="1" s="35"/>
-    <row r="776" ht="15.75" customHeight="1" s="35"/>
-    <row r="777" ht="15.75" customHeight="1" s="35"/>
-    <row r="778" ht="15.75" customHeight="1" s="35"/>
-    <row r="779" ht="15.75" customHeight="1" s="35"/>
-    <row r="780" ht="15.75" customHeight="1" s="35"/>
-    <row r="781" ht="15.75" customHeight="1" s="35"/>
-    <row r="782" ht="15.75" customHeight="1" s="35"/>
-    <row r="783" ht="15.75" customHeight="1" s="35"/>
-    <row r="784" ht="15.75" customHeight="1" s="35"/>
-    <row r="785" ht="15.75" customHeight="1" s="35"/>
-    <row r="786" ht="15.75" customHeight="1" s="35"/>
-    <row r="787" ht="15.75" customHeight="1" s="35"/>
-    <row r="788" ht="15.75" customHeight="1" s="35"/>
-    <row r="789" ht="15.75" customHeight="1" s="35"/>
-    <row r="790" ht="15.75" customHeight="1" s="35"/>
-    <row r="791" ht="15.75" customHeight="1" s="35"/>
-    <row r="792" ht="15.75" customHeight="1" s="35"/>
-    <row r="793" ht="15.75" customHeight="1" s="35"/>
-    <row r="794" ht="15.75" customHeight="1" s="35"/>
-    <row r="795" ht="15.75" customHeight="1" s="35"/>
-    <row r="796" ht="15.75" customHeight="1" s="35"/>
-    <row r="797" ht="15.75" customHeight="1" s="35"/>
-    <row r="798" ht="15.75" customHeight="1" s="35"/>
-    <row r="799" ht="15.75" customHeight="1" s="35"/>
-    <row r="800" ht="15.75" customHeight="1" s="35"/>
-    <row r="801" ht="15.75" customHeight="1" s="35"/>
-    <row r="802" ht="15.75" customHeight="1" s="35"/>
-    <row r="803" ht="15.75" customHeight="1" s="35"/>
-    <row r="804" ht="15.75" customHeight="1" s="35"/>
-    <row r="805" ht="15.75" customHeight="1" s="35"/>
-    <row r="806" ht="15.75" customHeight="1" s="35"/>
-    <row r="807" ht="15.75" customHeight="1" s="35"/>
-    <row r="808" ht="15.75" customHeight="1" s="35"/>
-    <row r="809" ht="15.75" customHeight="1" s="35"/>
-    <row r="810" ht="15.75" customHeight="1" s="35"/>
-    <row r="811" ht="15.75" customHeight="1" s="35"/>
-    <row r="812" ht="15.75" customHeight="1" s="35"/>
-    <row r="813" ht="15.75" customHeight="1" s="35"/>
-    <row r="814" ht="15.75" customHeight="1" s="35"/>
-    <row r="815" ht="15.75" customHeight="1" s="35"/>
-    <row r="816" ht="15.75" customHeight="1" s="35"/>
-    <row r="817" ht="15.75" customHeight="1" s="35"/>
-    <row r="818" ht="15.75" customHeight="1" s="35"/>
-    <row r="819" ht="15.75" customHeight="1" s="35"/>
-    <row r="820" ht="15.75" customHeight="1" s="35"/>
-    <row r="821" ht="15.75" customHeight="1" s="35"/>
-    <row r="822" ht="15.75" customHeight="1" s="35"/>
-    <row r="823" ht="15.75" customHeight="1" s="35"/>
-    <row r="824" ht="15.75" customHeight="1" s="35"/>
-    <row r="825" ht="15.75" customHeight="1" s="35"/>
-    <row r="826" ht="15.75" customHeight="1" s="35"/>
-    <row r="827" ht="15.75" customHeight="1" s="35"/>
-    <row r="828" ht="15.75" customHeight="1" s="35"/>
-    <row r="829" ht="15.75" customHeight="1" s="35"/>
-    <row r="830" ht="15.75" customHeight="1" s="35"/>
-    <row r="831" ht="15.75" customHeight="1" s="35"/>
-    <row r="832" ht="15.75" customHeight="1" s="35"/>
-    <row r="833" ht="15.75" customHeight="1" s="35"/>
-    <row r="834" ht="15.75" customHeight="1" s="35"/>
-    <row r="835" ht="15.75" customHeight="1" s="35"/>
-    <row r="836" ht="15.75" customHeight="1" s="35"/>
-    <row r="837" ht="15.75" customHeight="1" s="35"/>
-    <row r="838" ht="15.75" customHeight="1" s="35"/>
-    <row r="839" ht="15.75" customHeight="1" s="35"/>
-    <row r="840" ht="15.75" customHeight="1" s="35"/>
-    <row r="841" ht="15.75" customHeight="1" s="35"/>
-    <row r="842" ht="15.75" customHeight="1" s="35"/>
-    <row r="843" ht="15.75" customHeight="1" s="35"/>
-    <row r="844" ht="15.75" customHeight="1" s="35"/>
-    <row r="845" ht="15.75" customHeight="1" s="35"/>
-    <row r="846" ht="15.75" customHeight="1" s="35"/>
-    <row r="847" ht="15.75" customHeight="1" s="35"/>
-    <row r="848" ht="15.75" customHeight="1" s="35"/>
-    <row r="849" ht="15.75" customHeight="1" s="35"/>
-    <row r="850" ht="15.75" customHeight="1" s="35"/>
-    <row r="851" ht="15.75" customHeight="1" s="35"/>
-    <row r="852" ht="15.75" customHeight="1" s="35"/>
-    <row r="853" ht="15.75" customHeight="1" s="35"/>
-    <row r="854" ht="15.75" customHeight="1" s="35"/>
-    <row r="855" ht="15.75" customHeight="1" s="35"/>
-    <row r="856" ht="15.75" customHeight="1" s="35"/>
-    <row r="857" ht="15.75" customHeight="1" s="35"/>
-    <row r="858" ht="15.75" customHeight="1" s="35"/>
-    <row r="859" ht="15.75" customHeight="1" s="35"/>
-    <row r="860" ht="15.75" customHeight="1" s="35"/>
-    <row r="861" ht="15.75" customHeight="1" s="35"/>
-    <row r="862" ht="15.75" customHeight="1" s="35"/>
-    <row r="863" ht="15.75" customHeight="1" s="35"/>
-    <row r="864" ht="15.75" customHeight="1" s="35"/>
-    <row r="865" ht="15.75" customHeight="1" s="35"/>
-    <row r="866" ht="15.75" customHeight="1" s="35"/>
-    <row r="867" ht="15.75" customHeight="1" s="35"/>
-    <row r="868" ht="15.75" customHeight="1" s="35"/>
-    <row r="869" ht="15.75" customHeight="1" s="35"/>
-    <row r="870" ht="15.75" customHeight="1" s="35"/>
-    <row r="871" ht="15.75" customHeight="1" s="35"/>
-    <row r="872" ht="15.75" customHeight="1" s="35"/>
-    <row r="873" ht="15.75" customHeight="1" s="35"/>
-    <row r="874" ht="15.75" customHeight="1" s="35"/>
-    <row r="875" ht="15.75" customHeight="1" s="35"/>
-    <row r="876" ht="15.75" customHeight="1" s="35"/>
-    <row r="877" ht="15.75" customHeight="1" s="35"/>
-    <row r="878" ht="15.75" customHeight="1" s="35"/>
-    <row r="879" ht="15.75" customHeight="1" s="35"/>
-    <row r="880" ht="15.75" customHeight="1" s="35"/>
-    <row r="881" ht="15.75" customHeight="1" s="35"/>
-    <row r="882" ht="15.75" customHeight="1" s="35"/>
-    <row r="883" ht="15.75" customHeight="1" s="35"/>
-    <row r="884" ht="15.75" customHeight="1" s="35"/>
-    <row r="885" ht="15.75" customHeight="1" s="35"/>
-    <row r="886" ht="15.75" customHeight="1" s="35"/>
-    <row r="887" ht="15.75" customHeight="1" s="35"/>
-    <row r="888" ht="15.75" customHeight="1" s="35"/>
-    <row r="889" ht="15.75" customHeight="1" s="35"/>
-    <row r="890" ht="15.75" customHeight="1" s="35"/>
-    <row r="891" ht="15.75" customHeight="1" s="35"/>
-    <row r="892" ht="15.75" customHeight="1" s="35"/>
-    <row r="893" ht="15.75" customHeight="1" s="35"/>
-    <row r="894" ht="15.75" customHeight="1" s="35"/>
-    <row r="895" ht="15.75" customHeight="1" s="35"/>
-    <row r="896" ht="15.75" customHeight="1" s="35"/>
-    <row r="897" ht="15.75" customHeight="1" s="35"/>
-    <row r="898" ht="15.75" customHeight="1" s="35"/>
-    <row r="899" ht="15.75" customHeight="1" s="35"/>
-    <row r="900" ht="15.75" customHeight="1" s="35"/>
-    <row r="901" ht="15.75" customHeight="1" s="35"/>
-    <row r="902" ht="15.75" customHeight="1" s="35"/>
-    <row r="903" ht="15.75" customHeight="1" s="35"/>
-    <row r="904" ht="15.75" customHeight="1" s="35"/>
-    <row r="905" ht="15.75" customHeight="1" s="35"/>
-    <row r="906" ht="15.75" customHeight="1" s="35"/>
-    <row r="907" ht="15.75" customHeight="1" s="35"/>
-    <row r="908" ht="15.75" customHeight="1" s="35"/>
-    <row r="909" ht="15.75" customHeight="1" s="35"/>
-    <row r="910" ht="15.75" customHeight="1" s="35"/>
-    <row r="911" ht="15.75" customHeight="1" s="35"/>
-    <row r="912" ht="15.75" customHeight="1" s="35"/>
-    <row r="913" ht="15.75" customHeight="1" s="35"/>
-    <row r="914" ht="15.75" customHeight="1" s="35"/>
-    <row r="915" ht="15.75" customHeight="1" s="35"/>
-    <row r="916" ht="15.75" customHeight="1" s="35"/>
-    <row r="917" ht="15.75" customHeight="1" s="35"/>
-    <row r="918" ht="15.75" customHeight="1" s="35"/>
-    <row r="919" ht="15.75" customHeight="1" s="35"/>
-    <row r="920" ht="15.75" customHeight="1" s="35"/>
-    <row r="921" ht="15.75" customHeight="1" s="35"/>
-    <row r="922" ht="15.75" customHeight="1" s="35"/>
-    <row r="923" ht="15.75" customHeight="1" s="35"/>
-    <row r="924" ht="15.75" customHeight="1" s="35"/>
-    <row r="925" ht="15.75" customHeight="1" s="35"/>
-    <row r="926" ht="15.75" customHeight="1" s="35"/>
-    <row r="927" ht="15.75" customHeight="1" s="35"/>
-    <row r="928" ht="15.75" customHeight="1" s="35"/>
-    <row r="929" ht="15.75" customHeight="1" s="35"/>
-    <row r="930" ht="15.75" customHeight="1" s="35"/>
-    <row r="931" ht="15.75" customHeight="1" s="35"/>
-    <row r="932" ht="15.75" customHeight="1" s="35"/>
-    <row r="933" ht="15.75" customHeight="1" s="35"/>
-    <row r="934" ht="15.75" customHeight="1" s="35"/>
-    <row r="935" ht="15.75" customHeight="1" s="35"/>
-    <row r="936" ht="15.75" customHeight="1" s="35"/>
-    <row r="937" ht="15.75" customHeight="1" s="35"/>
-    <row r="938" ht="15.75" customHeight="1" s="35"/>
-    <row r="939" ht="15.75" customHeight="1" s="35"/>
-    <row r="940" ht="15.75" customHeight="1" s="35"/>
-    <row r="941" ht="15.75" customHeight="1" s="35"/>
-    <row r="942" ht="15.75" customHeight="1" s="35"/>
-    <row r="943" ht="15.75" customHeight="1" s="35"/>
-    <row r="944" ht="15.75" customHeight="1" s="35"/>
-    <row r="945" ht="15.75" customHeight="1" s="35"/>
-    <row r="946" ht="15.75" customHeight="1" s="35"/>
-    <row r="947" ht="15.75" customHeight="1" s="35"/>
-    <row r="948" ht="15.75" customHeight="1" s="35"/>
-    <row r="949" ht="15.75" customHeight="1" s="35"/>
-    <row r="950" ht="15.75" customHeight="1" s="35"/>
-    <row r="951" ht="15.75" customHeight="1" s="35"/>
-    <row r="952" ht="15.75" customHeight="1" s="35"/>
-    <row r="953" ht="15.75" customHeight="1" s="35"/>
-    <row r="954" ht="15.75" customHeight="1" s="35"/>
-    <row r="955" ht="15.75" customHeight="1" s="35"/>
-    <row r="956" ht="15.75" customHeight="1" s="35"/>
-    <row r="957" ht="15.75" customHeight="1" s="35"/>
-    <row r="958" ht="15.75" customHeight="1" s="35"/>
-    <row r="959" ht="15.75" customHeight="1" s="35"/>
-    <row r="960" ht="15.75" customHeight="1" s="35"/>
-    <row r="961" ht="15.75" customHeight="1" s="35"/>
-    <row r="962" ht="15.75" customHeight="1" s="35"/>
-    <row r="963" ht="15.75" customHeight="1" s="35"/>
-    <row r="964" ht="15.75" customHeight="1" s="35"/>
-    <row r="965" ht="15.75" customHeight="1" s="35"/>
-    <row r="966" ht="15.75" customHeight="1" s="35"/>
-    <row r="967" ht="15.75" customHeight="1" s="35"/>
-    <row r="968" ht="15.75" customHeight="1" s="35"/>
-    <row r="969" ht="15.75" customHeight="1" s="35"/>
-    <row r="970" ht="15.75" customHeight="1" s="35"/>
-    <row r="971" ht="15.75" customHeight="1" s="35"/>
-    <row r="972" ht="15.75" customHeight="1" s="35"/>
-    <row r="973" ht="15.75" customHeight="1" s="35"/>
-    <row r="974" ht="15.75" customHeight="1" s="35"/>
-    <row r="975" ht="15.75" customHeight="1" s="35"/>
-    <row r="976" ht="15.75" customHeight="1" s="35"/>
-    <row r="977" ht="15.75" customHeight="1" s="35"/>
-    <row r="978" ht="15.75" customHeight="1" s="35"/>
-    <row r="979" ht="15.75" customHeight="1" s="35"/>
-    <row r="980" ht="15.75" customHeight="1" s="35"/>
-    <row r="981" ht="15.75" customHeight="1" s="35"/>
-    <row r="982" ht="15.75" customHeight="1" s="35"/>
-    <row r="983" ht="15.75" customHeight="1" s="35"/>
-    <row r="984" ht="15.75" customHeight="1" s="35"/>
-    <row r="985" ht="15.75" customHeight="1" s="35"/>
-    <row r="986" ht="15.75" customHeight="1" s="35"/>
-    <row r="987" ht="15.75" customHeight="1" s="35"/>
-    <row r="988" ht="15.75" customHeight="1" s="35"/>
-    <row r="989" ht="15.75" customHeight="1" s="35"/>
-    <row r="990" ht="15.75" customHeight="1" s="35"/>
-    <row r="991" ht="15.75" customHeight="1" s="35"/>
-    <row r="992" ht="15.75" customHeight="1" s="35"/>
-    <row r="993" ht="15.75" customHeight="1" s="35"/>
-    <row r="994" ht="15.75" customHeight="1" s="35"/>
-    <row r="995" ht="15.75" customHeight="1" s="35"/>
-    <row r="996" ht="15.75" customHeight="1" s="35"/>
-    <row r="997" ht="15.75" customHeight="1" s="35"/>
-    <row r="998" ht="15.75" customHeight="1" s="35"/>
-    <row r="999" ht="15.75" customHeight="1" s="35"/>
-    <row r="1000" ht="15.75" customHeight="1" s="35"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -13612,45 +12327,48 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC18</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30.75" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="57.75" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="17.25" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Priya Raj (priya.raj@connectsphere.com / password123), Event Coordinator.
+'Kirana Regional Managers Offsite' and 'Straits Medical Research Symposium' are two different, already-submitted events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open 'All Events'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" s="35">
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Open 'All Events'
+2. Open 'Kirana Regional Managers Offsite' and note the reference shown next to its title
+3. Go back and open 'Straits Medical Research Symposium' and note its reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Events list page</t>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Events: Kirana Regional Managers Offsite, Straits Medical Research Symposium</t>
         </is>
       </c>
     </row>
@@ -13660,10 +12378,10 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Every row shows a 'Reference' column (e.g. 'EVT-000005') alongside Event, When, Attendance and Status.
-Clicking a row opens that event at the web address matching its reference.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Each event shows its own reference in the form 'EVT-######' next to its title, beside the status badge.
+The two events show two different references — the number is specific to that event, not a shared or repeated value.</t>
         </is>
       </c>
     </row>
@@ -13673,7 +12391,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13705,10 +12423,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Every row shows a 'Reference' column (e.g. 'EVT-000005') alongside Event, When, Attendance and Status.
-Clicking a row opens that event at the web address matching its reference.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Each event shows its own reference in the form 'EVT-######' next to its title, beside the status badge.
+The two events show two different references — the number is specific to that event, not a shared or repeated value.</t>
         </is>
       </c>
     </row>
@@ -13742,7 +12460,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13774,10 +12492,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Every row shows a 'Reference' column (e.g. 'EVT-000200') alongside Event, When, Attendance and Status.
-Clicking a row opens that event at the web address matching its reference.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Each event shows its own reference in the form 'EVT-######' next to its title, beside the status badge.
+The two events show two different references — the number is specific to that event, not a shared or repeated value.</t>
         </is>
       </c>
     </row>
@@ -13811,7 +12529,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14810,13 +13528,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="35" min="1" max="1"/>
@@ -14838,33 +13556,35 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.25" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC17</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.25" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator assigned to 'Meridian Wealth Management Forum' (status Confirmed, organised by James Koh, category Conference, expected attendance 150, preferred layout Theatre, registration enabled with capacity 150).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="17.25" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator assigned to 'Meridian Wealth Management Forum' (reference EVT-000005).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open 'Meridian Wealth Management Forum' from 'All Events'</t>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Open 'All Events'
+2. Open 'Meridian Wealth Management Forum'
+3. Look at the web address shown in the browser</t>
         </is>
       </c>
     </row>
@@ -14874,24 +13594,22 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Meridian Wealth Management Forum</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="165.75" customHeight="1" s="35">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Meridian Wealth Management Forum (EVT-000005)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>A reference such as 'EVT-000005' is shown next to the title, beside the 'Confirmed' status badge.
-The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
-The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
-The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The web address ends in '/EVT-000005' — a reference a person could read aloud or type from memory, not a long opaque id.
+Opening that same address directly (typed or bookmarked) loads the same event.</t>
         </is>
       </c>
     </row>
@@ -14901,7 +13619,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -14933,12 +13651,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>A reference such as 'EVT-000005' is shown next to the title, beside the 'Confirmed' status badge.
-The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
-The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
-The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The web address ends in '/EVT-000005' — a reference a person could read aloud or type from memory, not a long opaque id.
+Opening that same address directly (typed or bookmarked) loads the same event.</t>
         </is>
       </c>
     </row>
@@ -14972,7 +13688,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -15004,12 +13720,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>A reference such as 'EVT-000200' is shown next to the title, beside the 'Confirmed' status badge.
-The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
-The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
-The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The web address ends in '/EVT-000200' — a reference a person could read aloud or type from memory, not a long opaque id.
+Opening that same address directly (typed or bookmarked) loads the same event.</t>
         </is>
       </c>
     </row>
@@ -15043,7 +13757,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -15060,75 +13774,1423 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="35"/>
-    <row r="25" ht="15.75" customHeight="1" s="35">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="25" ht="15.75" customHeight="1" s="35"/>
+    <row r="26" ht="15.75" customHeight="1" s="35">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" s="35">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>A reference such as 'EVT-000005' is shown next to the title, beside the 'Confirmed' status badge.
-The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
-The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
-The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
-        </is>
-      </c>
+      <c r="B26" s="13" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="35">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>The web address ends in '/EVT-000005' — a reference a person could read aloud or type from memory, not a long opaque id.
+Opening that same address directly (typed or bookmarked) loads the same event.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="35">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Failed cases fixed by kristen on 2026-09-25</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="35">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Failed cases were fixed by Kristen on 2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="35">
       <c r="A30" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B30" s="39" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="35">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B31" s="17" t="n">
         <v>46290</v>
       </c>
     </row>
+    <row r="32" ht="15.75" customHeight="1" s="35"/>
+    <row r="33" ht="15.75" customHeight="1" s="35"/>
+    <row r="34" ht="15.75" customHeight="1" s="35"/>
+    <row r="35" ht="15.75" customHeight="1" s="35"/>
+    <row r="36" ht="15.75" customHeight="1" s="35"/>
+    <row r="37" ht="15.75" customHeight="1" s="35"/>
+    <row r="38" ht="15.75" customHeight="1" s="35"/>
+    <row r="39" ht="15.75" customHeight="1" s="35"/>
+    <row r="40" ht="15.75" customHeight="1" s="35"/>
+    <row r="41" ht="15.75" customHeight="1" s="35"/>
+    <row r="42" ht="15.75" customHeight="1" s="35"/>
+    <row r="43" ht="15.75" customHeight="1" s="35"/>
+    <row r="44" ht="15.75" customHeight="1" s="35"/>
+    <row r="45" ht="15.75" customHeight="1" s="35"/>
+    <row r="46" ht="15.75" customHeight="1" s="35"/>
+    <row r="47" ht="15.75" customHeight="1" s="35"/>
+    <row r="48" ht="15.75" customHeight="1" s="35"/>
+    <row r="49" ht="15.75" customHeight="1" s="35"/>
+    <row r="50" ht="15.75" customHeight="1" s="35"/>
+    <row r="51" ht="15.75" customHeight="1" s="35"/>
+    <row r="52" ht="15.75" customHeight="1" s="35"/>
+    <row r="53" ht="15.75" customHeight="1" s="35"/>
+    <row r="54" ht="15.75" customHeight="1" s="35"/>
+    <row r="55" ht="15.75" customHeight="1" s="35"/>
+    <row r="56" ht="15.75" customHeight="1" s="35"/>
+    <row r="57" ht="15.75" customHeight="1" s="35"/>
+    <row r="58" ht="15.75" customHeight="1" s="35"/>
+    <row r="59" ht="15.75" customHeight="1" s="35"/>
+    <row r="60" ht="15.75" customHeight="1" s="35"/>
+    <row r="61" ht="15.75" customHeight="1" s="35"/>
+    <row r="62" ht="15.75" customHeight="1" s="35"/>
+    <row r="63" ht="15.75" customHeight="1" s="35"/>
+    <row r="64" ht="15.75" customHeight="1" s="35"/>
+    <row r="65" ht="15.75" customHeight="1" s="35"/>
+    <row r="66" ht="15.75" customHeight="1" s="35"/>
+    <row r="67" ht="15.75" customHeight="1" s="35"/>
+    <row r="68" ht="15.75" customHeight="1" s="35"/>
+    <row r="69" ht="15.75" customHeight="1" s="35"/>
+    <row r="70" ht="15.75" customHeight="1" s="35"/>
+    <row r="71" ht="15.75" customHeight="1" s="35"/>
+    <row r="72" ht="15.75" customHeight="1" s="35"/>
+    <row r="73" ht="15.75" customHeight="1" s="35"/>
+    <row r="74" ht="15.75" customHeight="1" s="35"/>
+    <row r="75" ht="15.75" customHeight="1" s="35"/>
+    <row r="76" ht="15.75" customHeight="1" s="35"/>
+    <row r="77" ht="15.75" customHeight="1" s="35"/>
+    <row r="78" ht="15.75" customHeight="1" s="35"/>
+    <row r="79" ht="15.75" customHeight="1" s="35"/>
+    <row r="80" ht="15.75" customHeight="1" s="35"/>
+    <row r="81" ht="15.75" customHeight="1" s="35"/>
+    <row r="82" ht="15.75" customHeight="1" s="35"/>
+    <row r="83" ht="15.75" customHeight="1" s="35"/>
+    <row r="84" ht="15.75" customHeight="1" s="35"/>
+    <row r="85" ht="15.75" customHeight="1" s="35"/>
+    <row r="86" ht="15.75" customHeight="1" s="35"/>
+    <row r="87" ht="15.75" customHeight="1" s="35"/>
+    <row r="88" ht="15.75" customHeight="1" s="35"/>
+    <row r="89" ht="15.75" customHeight="1" s="35"/>
+    <row r="90" ht="15.75" customHeight="1" s="35"/>
+    <row r="91" ht="15.75" customHeight="1" s="35"/>
+    <row r="92" ht="15.75" customHeight="1" s="35"/>
+    <row r="93" ht="15.75" customHeight="1" s="35"/>
+    <row r="94" ht="15.75" customHeight="1" s="35"/>
+    <row r="95" ht="15.75" customHeight="1" s="35"/>
+    <row r="96" ht="15.75" customHeight="1" s="35"/>
+    <row r="97" ht="15.75" customHeight="1" s="35"/>
+    <row r="98" ht="15.75" customHeight="1" s="35"/>
+    <row r="99" ht="15.75" customHeight="1" s="35"/>
+    <row r="100" ht="15.75" customHeight="1" s="35"/>
+    <row r="101" ht="15.75" customHeight="1" s="35"/>
+    <row r="102" ht="15.75" customHeight="1" s="35"/>
+    <row r="103" ht="15.75" customHeight="1" s="35"/>
+    <row r="104" ht="15.75" customHeight="1" s="35"/>
+    <row r="105" ht="15.75" customHeight="1" s="35"/>
+    <row r="106" ht="15.75" customHeight="1" s="35"/>
+    <row r="107" ht="15.75" customHeight="1" s="35"/>
+    <row r="108" ht="15.75" customHeight="1" s="35"/>
+    <row r="109" ht="15.75" customHeight="1" s="35"/>
+    <row r="110" ht="15.75" customHeight="1" s="35"/>
+    <row r="111" ht="15.75" customHeight="1" s="35"/>
+    <row r="112" ht="15.75" customHeight="1" s="35"/>
+    <row r="113" ht="15.75" customHeight="1" s="35"/>
+    <row r="114" ht="15.75" customHeight="1" s="35"/>
+    <row r="115" ht="15.75" customHeight="1" s="35"/>
+    <row r="116" ht="15.75" customHeight="1" s="35"/>
+    <row r="117" ht="15.75" customHeight="1" s="35"/>
+    <row r="118" ht="15.75" customHeight="1" s="35"/>
+    <row r="119" ht="15.75" customHeight="1" s="35"/>
+    <row r="120" ht="15.75" customHeight="1" s="35"/>
+    <row r="121" ht="15.75" customHeight="1" s="35"/>
+    <row r="122" ht="15.75" customHeight="1" s="35"/>
+    <row r="123" ht="15.75" customHeight="1" s="35"/>
+    <row r="124" ht="15.75" customHeight="1" s="35"/>
+    <row r="125" ht="15.75" customHeight="1" s="35"/>
+    <row r="126" ht="15.75" customHeight="1" s="35"/>
+    <row r="127" ht="15.75" customHeight="1" s="35"/>
+    <row r="128" ht="15.75" customHeight="1" s="35"/>
+    <row r="129" ht="15.75" customHeight="1" s="35"/>
+    <row r="130" ht="15.75" customHeight="1" s="35"/>
+    <row r="131" ht="15.75" customHeight="1" s="35"/>
+    <row r="132" ht="15.75" customHeight="1" s="35"/>
+    <row r="133" ht="15.75" customHeight="1" s="35"/>
+    <row r="134" ht="15.75" customHeight="1" s="35"/>
+    <row r="135" ht="15.75" customHeight="1" s="35"/>
+    <row r="136" ht="15.75" customHeight="1" s="35"/>
+    <row r="137" ht="15.75" customHeight="1" s="35"/>
+    <row r="138" ht="15.75" customHeight="1" s="35"/>
+    <row r="139" ht="15.75" customHeight="1" s="35"/>
+    <row r="140" ht="15.75" customHeight="1" s="35"/>
+    <row r="141" ht="15.75" customHeight="1" s="35"/>
+    <row r="142" ht="15.75" customHeight="1" s="35"/>
+    <row r="143" ht="15.75" customHeight="1" s="35"/>
+    <row r="144" ht="15.75" customHeight="1" s="35"/>
+    <row r="145" ht="15.75" customHeight="1" s="35"/>
+    <row r="146" ht="15.75" customHeight="1" s="35"/>
+    <row r="147" ht="15.75" customHeight="1" s="35"/>
+    <row r="148" ht="15.75" customHeight="1" s="35"/>
+    <row r="149" ht="15.75" customHeight="1" s="35"/>
+    <row r="150" ht="15.75" customHeight="1" s="35"/>
+    <row r="151" ht="15.75" customHeight="1" s="35"/>
+    <row r="152" ht="15.75" customHeight="1" s="35"/>
+    <row r="153" ht="15.75" customHeight="1" s="35"/>
+    <row r="154" ht="15.75" customHeight="1" s="35"/>
+    <row r="155" ht="15.75" customHeight="1" s="35"/>
+    <row r="156" ht="15.75" customHeight="1" s="35"/>
+    <row r="157" ht="15.75" customHeight="1" s="35"/>
+    <row r="158" ht="15.75" customHeight="1" s="35"/>
+    <row r="159" ht="15.75" customHeight="1" s="35"/>
+    <row r="160" ht="15.75" customHeight="1" s="35"/>
+    <row r="161" ht="15.75" customHeight="1" s="35"/>
+    <row r="162" ht="15.75" customHeight="1" s="35"/>
+    <row r="163" ht="15.75" customHeight="1" s="35"/>
+    <row r="164" ht="15.75" customHeight="1" s="35"/>
+    <row r="165" ht="15.75" customHeight="1" s="35"/>
+    <row r="166" ht="15.75" customHeight="1" s="35"/>
+    <row r="167" ht="15.75" customHeight="1" s="35"/>
+    <row r="168" ht="15.75" customHeight="1" s="35"/>
+    <row r="169" ht="15.75" customHeight="1" s="35"/>
+    <row r="170" ht="15.75" customHeight="1" s="35"/>
+    <row r="171" ht="15.75" customHeight="1" s="35"/>
+    <row r="172" ht="15.75" customHeight="1" s="35"/>
+    <row r="173" ht="15.75" customHeight="1" s="35"/>
+    <row r="174" ht="15.75" customHeight="1" s="35"/>
+    <row r="175" ht="15.75" customHeight="1" s="35"/>
+    <row r="176" ht="15.75" customHeight="1" s="35"/>
+    <row r="177" ht="15.75" customHeight="1" s="35"/>
+    <row r="178" ht="15.75" customHeight="1" s="35"/>
+    <row r="179" ht="15.75" customHeight="1" s="35"/>
+    <row r="180" ht="15.75" customHeight="1" s="35"/>
+    <row r="181" ht="15.75" customHeight="1" s="35"/>
+    <row r="182" ht="15.75" customHeight="1" s="35"/>
+    <row r="183" ht="15.75" customHeight="1" s="35"/>
+    <row r="184" ht="15.75" customHeight="1" s="35"/>
+    <row r="185" ht="15.75" customHeight="1" s="35"/>
+    <row r="186" ht="15.75" customHeight="1" s="35"/>
+    <row r="187" ht="15.75" customHeight="1" s="35"/>
+    <row r="188" ht="15.75" customHeight="1" s="35"/>
+    <row r="189" ht="15.75" customHeight="1" s="35"/>
+    <row r="190" ht="15.75" customHeight="1" s="35"/>
+    <row r="191" ht="15.75" customHeight="1" s="35"/>
+    <row r="192" ht="15.75" customHeight="1" s="35"/>
+    <row r="193" ht="15.75" customHeight="1" s="35"/>
+    <row r="194" ht="15.75" customHeight="1" s="35"/>
+    <row r="195" ht="15.75" customHeight="1" s="35"/>
+    <row r="196" ht="15.75" customHeight="1" s="35"/>
+    <row r="197" ht="15.75" customHeight="1" s="35"/>
+    <row r="198" ht="15.75" customHeight="1" s="35"/>
+    <row r="199" ht="15.75" customHeight="1" s="35"/>
+    <row r="200" ht="15.75" customHeight="1" s="35"/>
+    <row r="201" ht="15.75" customHeight="1" s="35"/>
+    <row r="202" ht="15.75" customHeight="1" s="35"/>
+    <row r="203" ht="15.75" customHeight="1" s="35"/>
+    <row r="204" ht="15.75" customHeight="1" s="35"/>
+    <row r="205" ht="15.75" customHeight="1" s="35"/>
+    <row r="206" ht="15.75" customHeight="1" s="35"/>
+    <row r="207" ht="15.75" customHeight="1" s="35"/>
+    <row r="208" ht="15.75" customHeight="1" s="35"/>
+    <row r="209" ht="15.75" customHeight="1" s="35"/>
+    <row r="210" ht="15.75" customHeight="1" s="35"/>
+    <row r="211" ht="15.75" customHeight="1" s="35"/>
+    <row r="212" ht="15.75" customHeight="1" s="35"/>
+    <row r="213" ht="15.75" customHeight="1" s="35"/>
+    <row r="214" ht="15.75" customHeight="1" s="35"/>
+    <row r="215" ht="15.75" customHeight="1" s="35"/>
+    <row r="216" ht="15.75" customHeight="1" s="35"/>
+    <row r="217" ht="15.75" customHeight="1" s="35"/>
+    <row r="218" ht="15.75" customHeight="1" s="35"/>
+    <row r="219" ht="15.75" customHeight="1" s="35"/>
+    <row r="220" ht="15.75" customHeight="1" s="35"/>
+    <row r="221" ht="15.75" customHeight="1" s="35"/>
+    <row r="222" ht="15.75" customHeight="1" s="35"/>
+    <row r="223" ht="15.75" customHeight="1" s="35"/>
+    <row r="224" ht="15.75" customHeight="1" s="35"/>
+    <row r="225" ht="15.75" customHeight="1" s="35"/>
+    <row r="226" ht="15.75" customHeight="1" s="35"/>
+    <row r="227" ht="15.75" customHeight="1" s="35"/>
+    <row r="228" ht="15.75" customHeight="1" s="35"/>
+    <row r="229" ht="15.75" customHeight="1" s="35"/>
+    <row r="230" ht="15.75" customHeight="1" s="35"/>
+    <row r="231" ht="15.75" customHeight="1" s="35"/>
+    <row r="232" ht="15.75" customHeight="1" s="35"/>
+    <row r="233" ht="15.75" customHeight="1" s="35"/>
+    <row r="234" ht="15.75" customHeight="1" s="35"/>
+    <row r="235" ht="15.75" customHeight="1" s="35"/>
+    <row r="236" ht="15.75" customHeight="1" s="35"/>
+    <row r="237" ht="15.75" customHeight="1" s="35"/>
+    <row r="238" ht="15.75" customHeight="1" s="35"/>
+    <row r="239" ht="15.75" customHeight="1" s="35"/>
+    <row r="240" ht="15.75" customHeight="1" s="35"/>
+    <row r="241" ht="15.75" customHeight="1" s="35"/>
+    <row r="242" ht="15.75" customHeight="1" s="35"/>
+    <row r="243" ht="15.75" customHeight="1" s="35"/>
+    <row r="244" ht="15.75" customHeight="1" s="35"/>
+    <row r="245" ht="15.75" customHeight="1" s="35"/>
+    <row r="246" ht="15.75" customHeight="1" s="35"/>
+    <row r="247" ht="15.75" customHeight="1" s="35"/>
+    <row r="248" ht="15.75" customHeight="1" s="35"/>
+    <row r="249" ht="15.75" customHeight="1" s="35"/>
+    <row r="250" ht="15.75" customHeight="1" s="35"/>
+    <row r="251" ht="15.75" customHeight="1" s="35"/>
+    <row r="252" ht="15.75" customHeight="1" s="35"/>
+    <row r="253" ht="15.75" customHeight="1" s="35"/>
+    <row r="254" ht="15.75" customHeight="1" s="35"/>
+    <row r="255" ht="15.75" customHeight="1" s="35"/>
+    <row r="256" ht="15.75" customHeight="1" s="35"/>
+    <row r="257" ht="15.75" customHeight="1" s="35"/>
+    <row r="258" ht="15.75" customHeight="1" s="35"/>
+    <row r="259" ht="15.75" customHeight="1" s="35"/>
+    <row r="260" ht="15.75" customHeight="1" s="35"/>
+    <row r="261" ht="15.75" customHeight="1" s="35"/>
+    <row r="262" ht="15.75" customHeight="1" s="35"/>
+    <row r="263" ht="15.75" customHeight="1" s="35"/>
+    <row r="264" ht="15.75" customHeight="1" s="35"/>
+    <row r="265" ht="15.75" customHeight="1" s="35"/>
+    <row r="266" ht="15.75" customHeight="1" s="35"/>
+    <row r="267" ht="15.75" customHeight="1" s="35"/>
+    <row r="268" ht="15.75" customHeight="1" s="35"/>
+    <row r="269" ht="15.75" customHeight="1" s="35"/>
+    <row r="270" ht="15.75" customHeight="1" s="35"/>
+    <row r="271" ht="15.75" customHeight="1" s="35"/>
+    <row r="272" ht="15.75" customHeight="1" s="35"/>
+    <row r="273" ht="15.75" customHeight="1" s="35"/>
+    <row r="274" ht="15.75" customHeight="1" s="35"/>
+    <row r="275" ht="15.75" customHeight="1" s="35"/>
+    <row r="276" ht="15.75" customHeight="1" s="35"/>
+    <row r="277" ht="15.75" customHeight="1" s="35"/>
+    <row r="278" ht="15.75" customHeight="1" s="35"/>
+    <row r="279" ht="15.75" customHeight="1" s="35"/>
+    <row r="280" ht="15.75" customHeight="1" s="35"/>
+    <row r="281" ht="15.75" customHeight="1" s="35"/>
+    <row r="282" ht="15.75" customHeight="1" s="35"/>
+    <row r="283" ht="15.75" customHeight="1" s="35"/>
+    <row r="284" ht="15.75" customHeight="1" s="35"/>
+    <row r="285" ht="15.75" customHeight="1" s="35"/>
+    <row r="286" ht="15.75" customHeight="1" s="35"/>
+    <row r="287" ht="15.75" customHeight="1" s="35"/>
+    <row r="288" ht="15.75" customHeight="1" s="35"/>
+    <row r="289" ht="15.75" customHeight="1" s="35"/>
+    <row r="290" ht="15.75" customHeight="1" s="35"/>
+    <row r="291" ht="15.75" customHeight="1" s="35"/>
+    <row r="292" ht="15.75" customHeight="1" s="35"/>
+    <row r="293" ht="15.75" customHeight="1" s="35"/>
+    <row r="294" ht="15.75" customHeight="1" s="35"/>
+    <row r="295" ht="15.75" customHeight="1" s="35"/>
+    <row r="296" ht="15.75" customHeight="1" s="35"/>
+    <row r="297" ht="15.75" customHeight="1" s="35"/>
+    <row r="298" ht="15.75" customHeight="1" s="35"/>
+    <row r="299" ht="15.75" customHeight="1" s="35"/>
+    <row r="300" ht="15.75" customHeight="1" s="35"/>
+    <row r="301" ht="15.75" customHeight="1" s="35"/>
+    <row r="302" ht="15.75" customHeight="1" s="35"/>
+    <row r="303" ht="15.75" customHeight="1" s="35"/>
+    <row r="304" ht="15.75" customHeight="1" s="35"/>
+    <row r="305" ht="15.75" customHeight="1" s="35"/>
+    <row r="306" ht="15.75" customHeight="1" s="35"/>
+    <row r="307" ht="15.75" customHeight="1" s="35"/>
+    <row r="308" ht="15.75" customHeight="1" s="35"/>
+    <row r="309" ht="15.75" customHeight="1" s="35"/>
+    <row r="310" ht="15.75" customHeight="1" s="35"/>
+    <row r="311" ht="15.75" customHeight="1" s="35"/>
+    <row r="312" ht="15.75" customHeight="1" s="35"/>
+    <row r="313" ht="15.75" customHeight="1" s="35"/>
+    <row r="314" ht="15.75" customHeight="1" s="35"/>
+    <row r="315" ht="15.75" customHeight="1" s="35"/>
+    <row r="316" ht="15.75" customHeight="1" s="35"/>
+    <row r="317" ht="15.75" customHeight="1" s="35"/>
+    <row r="318" ht="15.75" customHeight="1" s="35"/>
+    <row r="319" ht="15.75" customHeight="1" s="35"/>
+    <row r="320" ht="15.75" customHeight="1" s="35"/>
+    <row r="321" ht="15.75" customHeight="1" s="35"/>
+    <row r="322" ht="15.75" customHeight="1" s="35"/>
+    <row r="323" ht="15.75" customHeight="1" s="35"/>
+    <row r="324" ht="15.75" customHeight="1" s="35"/>
+    <row r="325" ht="15.75" customHeight="1" s="35"/>
+    <row r="326" ht="15.75" customHeight="1" s="35"/>
+    <row r="327" ht="15.75" customHeight="1" s="35"/>
+    <row r="328" ht="15.75" customHeight="1" s="35"/>
+    <row r="329" ht="15.75" customHeight="1" s="35"/>
+    <row r="330" ht="15.75" customHeight="1" s="35"/>
+    <row r="331" ht="15.75" customHeight="1" s="35"/>
+    <row r="332" ht="15.75" customHeight="1" s="35"/>
+    <row r="333" ht="15.75" customHeight="1" s="35"/>
+    <row r="334" ht="15.75" customHeight="1" s="35"/>
+    <row r="335" ht="15.75" customHeight="1" s="35"/>
+    <row r="336" ht="15.75" customHeight="1" s="35"/>
+    <row r="337" ht="15.75" customHeight="1" s="35"/>
+    <row r="338" ht="15.75" customHeight="1" s="35"/>
+    <row r="339" ht="15.75" customHeight="1" s="35"/>
+    <row r="340" ht="15.75" customHeight="1" s="35"/>
+    <row r="341" ht="15.75" customHeight="1" s="35"/>
+    <row r="342" ht="15.75" customHeight="1" s="35"/>
+    <row r="343" ht="15.75" customHeight="1" s="35"/>
+    <row r="344" ht="15.75" customHeight="1" s="35"/>
+    <row r="345" ht="15.75" customHeight="1" s="35"/>
+    <row r="346" ht="15.75" customHeight="1" s="35"/>
+    <row r="347" ht="15.75" customHeight="1" s="35"/>
+    <row r="348" ht="15.75" customHeight="1" s="35"/>
+    <row r="349" ht="15.75" customHeight="1" s="35"/>
+    <row r="350" ht="15.75" customHeight="1" s="35"/>
+    <row r="351" ht="15.75" customHeight="1" s="35"/>
+    <row r="352" ht="15.75" customHeight="1" s="35"/>
+    <row r="353" ht="15.75" customHeight="1" s="35"/>
+    <row r="354" ht="15.75" customHeight="1" s="35"/>
+    <row r="355" ht="15.75" customHeight="1" s="35"/>
+    <row r="356" ht="15.75" customHeight="1" s="35"/>
+    <row r="357" ht="15.75" customHeight="1" s="35"/>
+    <row r="358" ht="15.75" customHeight="1" s="35"/>
+    <row r="359" ht="15.75" customHeight="1" s="35"/>
+    <row r="360" ht="15.75" customHeight="1" s="35"/>
+    <row r="361" ht="15.75" customHeight="1" s="35"/>
+    <row r="362" ht="15.75" customHeight="1" s="35"/>
+    <row r="363" ht="15.75" customHeight="1" s="35"/>
+    <row r="364" ht="15.75" customHeight="1" s="35"/>
+    <row r="365" ht="15.75" customHeight="1" s="35"/>
+    <row r="366" ht="15.75" customHeight="1" s="35"/>
+    <row r="367" ht="15.75" customHeight="1" s="35"/>
+    <row r="368" ht="15.75" customHeight="1" s="35"/>
+    <row r="369" ht="15.75" customHeight="1" s="35"/>
+    <row r="370" ht="15.75" customHeight="1" s="35"/>
+    <row r="371" ht="15.75" customHeight="1" s="35"/>
+    <row r="372" ht="15.75" customHeight="1" s="35"/>
+    <row r="373" ht="15.75" customHeight="1" s="35"/>
+    <row r="374" ht="15.75" customHeight="1" s="35"/>
+    <row r="375" ht="15.75" customHeight="1" s="35"/>
+    <row r="376" ht="15.75" customHeight="1" s="35"/>
+    <row r="377" ht="15.75" customHeight="1" s="35"/>
+    <row r="378" ht="15.75" customHeight="1" s="35"/>
+    <row r="379" ht="15.75" customHeight="1" s="35"/>
+    <row r="380" ht="15.75" customHeight="1" s="35"/>
+    <row r="381" ht="15.75" customHeight="1" s="35"/>
+    <row r="382" ht="15.75" customHeight="1" s="35"/>
+    <row r="383" ht="15.75" customHeight="1" s="35"/>
+    <row r="384" ht="15.75" customHeight="1" s="35"/>
+    <row r="385" ht="15.75" customHeight="1" s="35"/>
+    <row r="386" ht="15.75" customHeight="1" s="35"/>
+    <row r="387" ht="15.75" customHeight="1" s="35"/>
+    <row r="388" ht="15.75" customHeight="1" s="35"/>
+    <row r="389" ht="15.75" customHeight="1" s="35"/>
+    <row r="390" ht="15.75" customHeight="1" s="35"/>
+    <row r="391" ht="15.75" customHeight="1" s="35"/>
+    <row r="392" ht="15.75" customHeight="1" s="35"/>
+    <row r="393" ht="15.75" customHeight="1" s="35"/>
+    <row r="394" ht="15.75" customHeight="1" s="35"/>
+    <row r="395" ht="15.75" customHeight="1" s="35"/>
+    <row r="396" ht="15.75" customHeight="1" s="35"/>
+    <row r="397" ht="15.75" customHeight="1" s="35"/>
+    <row r="398" ht="15.75" customHeight="1" s="35"/>
+    <row r="399" ht="15.75" customHeight="1" s="35"/>
+    <row r="400" ht="15.75" customHeight="1" s="35"/>
+    <row r="401" ht="15.75" customHeight="1" s="35"/>
+    <row r="402" ht="15.75" customHeight="1" s="35"/>
+    <row r="403" ht="15.75" customHeight="1" s="35"/>
+    <row r="404" ht="15.75" customHeight="1" s="35"/>
+    <row r="405" ht="15.75" customHeight="1" s="35"/>
+    <row r="406" ht="15.75" customHeight="1" s="35"/>
+    <row r="407" ht="15.75" customHeight="1" s="35"/>
+    <row r="408" ht="15.75" customHeight="1" s="35"/>
+    <row r="409" ht="15.75" customHeight="1" s="35"/>
+    <row r="410" ht="15.75" customHeight="1" s="35"/>
+    <row r="411" ht="15.75" customHeight="1" s="35"/>
+    <row r="412" ht="15.75" customHeight="1" s="35"/>
+    <row r="413" ht="15.75" customHeight="1" s="35"/>
+    <row r="414" ht="15.75" customHeight="1" s="35"/>
+    <row r="415" ht="15.75" customHeight="1" s="35"/>
+    <row r="416" ht="15.75" customHeight="1" s="35"/>
+    <row r="417" ht="15.75" customHeight="1" s="35"/>
+    <row r="418" ht="15.75" customHeight="1" s="35"/>
+    <row r="419" ht="15.75" customHeight="1" s="35"/>
+    <row r="420" ht="15.75" customHeight="1" s="35"/>
+    <row r="421" ht="15.75" customHeight="1" s="35"/>
+    <row r="422" ht="15.75" customHeight="1" s="35"/>
+    <row r="423" ht="15.75" customHeight="1" s="35"/>
+    <row r="424" ht="15.75" customHeight="1" s="35"/>
+    <row r="425" ht="15.75" customHeight="1" s="35"/>
+    <row r="426" ht="15.75" customHeight="1" s="35"/>
+    <row r="427" ht="15.75" customHeight="1" s="35"/>
+    <row r="428" ht="15.75" customHeight="1" s="35"/>
+    <row r="429" ht="15.75" customHeight="1" s="35"/>
+    <row r="430" ht="15.75" customHeight="1" s="35"/>
+    <row r="431" ht="15.75" customHeight="1" s="35"/>
+    <row r="432" ht="15.75" customHeight="1" s="35"/>
+    <row r="433" ht="15.75" customHeight="1" s="35"/>
+    <row r="434" ht="15.75" customHeight="1" s="35"/>
+    <row r="435" ht="15.75" customHeight="1" s="35"/>
+    <row r="436" ht="15.75" customHeight="1" s="35"/>
+    <row r="437" ht="15.75" customHeight="1" s="35"/>
+    <row r="438" ht="15.75" customHeight="1" s="35"/>
+    <row r="439" ht="15.75" customHeight="1" s="35"/>
+    <row r="440" ht="15.75" customHeight="1" s="35"/>
+    <row r="441" ht="15.75" customHeight="1" s="35"/>
+    <row r="442" ht="15.75" customHeight="1" s="35"/>
+    <row r="443" ht="15.75" customHeight="1" s="35"/>
+    <row r="444" ht="15.75" customHeight="1" s="35"/>
+    <row r="445" ht="15.75" customHeight="1" s="35"/>
+    <row r="446" ht="15.75" customHeight="1" s="35"/>
+    <row r="447" ht="15.75" customHeight="1" s="35"/>
+    <row r="448" ht="15.75" customHeight="1" s="35"/>
+    <row r="449" ht="15.75" customHeight="1" s="35"/>
+    <row r="450" ht="15.75" customHeight="1" s="35"/>
+    <row r="451" ht="15.75" customHeight="1" s="35"/>
+    <row r="452" ht="15.75" customHeight="1" s="35"/>
+    <row r="453" ht="15.75" customHeight="1" s="35"/>
+    <row r="454" ht="15.75" customHeight="1" s="35"/>
+    <row r="455" ht="15.75" customHeight="1" s="35"/>
+    <row r="456" ht="15.75" customHeight="1" s="35"/>
+    <row r="457" ht="15.75" customHeight="1" s="35"/>
+    <row r="458" ht="15.75" customHeight="1" s="35"/>
+    <row r="459" ht="15.75" customHeight="1" s="35"/>
+    <row r="460" ht="15.75" customHeight="1" s="35"/>
+    <row r="461" ht="15.75" customHeight="1" s="35"/>
+    <row r="462" ht="15.75" customHeight="1" s="35"/>
+    <row r="463" ht="15.75" customHeight="1" s="35"/>
+    <row r="464" ht="15.75" customHeight="1" s="35"/>
+    <row r="465" ht="15.75" customHeight="1" s="35"/>
+    <row r="466" ht="15.75" customHeight="1" s="35"/>
+    <row r="467" ht="15.75" customHeight="1" s="35"/>
+    <row r="468" ht="15.75" customHeight="1" s="35"/>
+    <row r="469" ht="15.75" customHeight="1" s="35"/>
+    <row r="470" ht="15.75" customHeight="1" s="35"/>
+    <row r="471" ht="15.75" customHeight="1" s="35"/>
+    <row r="472" ht="15.75" customHeight="1" s="35"/>
+    <row r="473" ht="15.75" customHeight="1" s="35"/>
+    <row r="474" ht="15.75" customHeight="1" s="35"/>
+    <row r="475" ht="15.75" customHeight="1" s="35"/>
+    <row r="476" ht="15.75" customHeight="1" s="35"/>
+    <row r="477" ht="15.75" customHeight="1" s="35"/>
+    <row r="478" ht="15.75" customHeight="1" s="35"/>
+    <row r="479" ht="15.75" customHeight="1" s="35"/>
+    <row r="480" ht="15.75" customHeight="1" s="35"/>
+    <row r="481" ht="15.75" customHeight="1" s="35"/>
+    <row r="482" ht="15.75" customHeight="1" s="35"/>
+    <row r="483" ht="15.75" customHeight="1" s="35"/>
+    <row r="484" ht="15.75" customHeight="1" s="35"/>
+    <row r="485" ht="15.75" customHeight="1" s="35"/>
+    <row r="486" ht="15.75" customHeight="1" s="35"/>
+    <row r="487" ht="15.75" customHeight="1" s="35"/>
+    <row r="488" ht="15.75" customHeight="1" s="35"/>
+    <row r="489" ht="15.75" customHeight="1" s="35"/>
+    <row r="490" ht="15.75" customHeight="1" s="35"/>
+    <row r="491" ht="15.75" customHeight="1" s="35"/>
+    <row r="492" ht="15.75" customHeight="1" s="35"/>
+    <row r="493" ht="15.75" customHeight="1" s="35"/>
+    <row r="494" ht="15.75" customHeight="1" s="35"/>
+    <row r="495" ht="15.75" customHeight="1" s="35"/>
+    <row r="496" ht="15.75" customHeight="1" s="35"/>
+    <row r="497" ht="15.75" customHeight="1" s="35"/>
+    <row r="498" ht="15.75" customHeight="1" s="35"/>
+    <row r="499" ht="15.75" customHeight="1" s="35"/>
+    <row r="500" ht="15.75" customHeight="1" s="35"/>
+    <row r="501" ht="15.75" customHeight="1" s="35"/>
+    <row r="502" ht="15.75" customHeight="1" s="35"/>
+    <row r="503" ht="15.75" customHeight="1" s="35"/>
+    <row r="504" ht="15.75" customHeight="1" s="35"/>
+    <row r="505" ht="15.75" customHeight="1" s="35"/>
+    <row r="506" ht="15.75" customHeight="1" s="35"/>
+    <row r="507" ht="15.75" customHeight="1" s="35"/>
+    <row r="508" ht="15.75" customHeight="1" s="35"/>
+    <row r="509" ht="15.75" customHeight="1" s="35"/>
+    <row r="510" ht="15.75" customHeight="1" s="35"/>
+    <row r="511" ht="15.75" customHeight="1" s="35"/>
+    <row r="512" ht="15.75" customHeight="1" s="35"/>
+    <row r="513" ht="15.75" customHeight="1" s="35"/>
+    <row r="514" ht="15.75" customHeight="1" s="35"/>
+    <row r="515" ht="15.75" customHeight="1" s="35"/>
+    <row r="516" ht="15.75" customHeight="1" s="35"/>
+    <row r="517" ht="15.75" customHeight="1" s="35"/>
+    <row r="518" ht="15.75" customHeight="1" s="35"/>
+    <row r="519" ht="15.75" customHeight="1" s="35"/>
+    <row r="520" ht="15.75" customHeight="1" s="35"/>
+    <row r="521" ht="15.75" customHeight="1" s="35"/>
+    <row r="522" ht="15.75" customHeight="1" s="35"/>
+    <row r="523" ht="15.75" customHeight="1" s="35"/>
+    <row r="524" ht="15.75" customHeight="1" s="35"/>
+    <row r="525" ht="15.75" customHeight="1" s="35"/>
+    <row r="526" ht="15.75" customHeight="1" s="35"/>
+    <row r="527" ht="15.75" customHeight="1" s="35"/>
+    <row r="528" ht="15.75" customHeight="1" s="35"/>
+    <row r="529" ht="15.75" customHeight="1" s="35"/>
+    <row r="530" ht="15.75" customHeight="1" s="35"/>
+    <row r="531" ht="15.75" customHeight="1" s="35"/>
+    <row r="532" ht="15.75" customHeight="1" s="35"/>
+    <row r="533" ht="15.75" customHeight="1" s="35"/>
+    <row r="534" ht="15.75" customHeight="1" s="35"/>
+    <row r="535" ht="15.75" customHeight="1" s="35"/>
+    <row r="536" ht="15.75" customHeight="1" s="35"/>
+    <row r="537" ht="15.75" customHeight="1" s="35"/>
+    <row r="538" ht="15.75" customHeight="1" s="35"/>
+    <row r="539" ht="15.75" customHeight="1" s="35"/>
+    <row r="540" ht="15.75" customHeight="1" s="35"/>
+    <row r="541" ht="15.75" customHeight="1" s="35"/>
+    <row r="542" ht="15.75" customHeight="1" s="35"/>
+    <row r="543" ht="15.75" customHeight="1" s="35"/>
+    <row r="544" ht="15.75" customHeight="1" s="35"/>
+    <row r="545" ht="15.75" customHeight="1" s="35"/>
+    <row r="546" ht="15.75" customHeight="1" s="35"/>
+    <row r="547" ht="15.75" customHeight="1" s="35"/>
+    <row r="548" ht="15.75" customHeight="1" s="35"/>
+    <row r="549" ht="15.75" customHeight="1" s="35"/>
+    <row r="550" ht="15.75" customHeight="1" s="35"/>
+    <row r="551" ht="15.75" customHeight="1" s="35"/>
+    <row r="552" ht="15.75" customHeight="1" s="35"/>
+    <row r="553" ht="15.75" customHeight="1" s="35"/>
+    <row r="554" ht="15.75" customHeight="1" s="35"/>
+    <row r="555" ht="15.75" customHeight="1" s="35"/>
+    <row r="556" ht="15.75" customHeight="1" s="35"/>
+    <row r="557" ht="15.75" customHeight="1" s="35"/>
+    <row r="558" ht="15.75" customHeight="1" s="35"/>
+    <row r="559" ht="15.75" customHeight="1" s="35"/>
+    <row r="560" ht="15.75" customHeight="1" s="35"/>
+    <row r="561" ht="15.75" customHeight="1" s="35"/>
+    <row r="562" ht="15.75" customHeight="1" s="35"/>
+    <row r="563" ht="15.75" customHeight="1" s="35"/>
+    <row r="564" ht="15.75" customHeight="1" s="35"/>
+    <row r="565" ht="15.75" customHeight="1" s="35"/>
+    <row r="566" ht="15.75" customHeight="1" s="35"/>
+    <row r="567" ht="15.75" customHeight="1" s="35"/>
+    <row r="568" ht="15.75" customHeight="1" s="35"/>
+    <row r="569" ht="15.75" customHeight="1" s="35"/>
+    <row r="570" ht="15.75" customHeight="1" s="35"/>
+    <row r="571" ht="15.75" customHeight="1" s="35"/>
+    <row r="572" ht="15.75" customHeight="1" s="35"/>
+    <row r="573" ht="15.75" customHeight="1" s="35"/>
+    <row r="574" ht="15.75" customHeight="1" s="35"/>
+    <row r="575" ht="15.75" customHeight="1" s="35"/>
+    <row r="576" ht="15.75" customHeight="1" s="35"/>
+    <row r="577" ht="15.75" customHeight="1" s="35"/>
+    <row r="578" ht="15.75" customHeight="1" s="35"/>
+    <row r="579" ht="15.75" customHeight="1" s="35"/>
+    <row r="580" ht="15.75" customHeight="1" s="35"/>
+    <row r="581" ht="15.75" customHeight="1" s="35"/>
+    <row r="582" ht="15.75" customHeight="1" s="35"/>
+    <row r="583" ht="15.75" customHeight="1" s="35"/>
+    <row r="584" ht="15.75" customHeight="1" s="35"/>
+    <row r="585" ht="15.75" customHeight="1" s="35"/>
+    <row r="586" ht="15.75" customHeight="1" s="35"/>
+    <row r="587" ht="15.75" customHeight="1" s="35"/>
+    <row r="588" ht="15.75" customHeight="1" s="35"/>
+    <row r="589" ht="15.75" customHeight="1" s="35"/>
+    <row r="590" ht="15.75" customHeight="1" s="35"/>
+    <row r="591" ht="15.75" customHeight="1" s="35"/>
+    <row r="592" ht="15.75" customHeight="1" s="35"/>
+    <row r="593" ht="15.75" customHeight="1" s="35"/>
+    <row r="594" ht="15.75" customHeight="1" s="35"/>
+    <row r="595" ht="15.75" customHeight="1" s="35"/>
+    <row r="596" ht="15.75" customHeight="1" s="35"/>
+    <row r="597" ht="15.75" customHeight="1" s="35"/>
+    <row r="598" ht="15.75" customHeight="1" s="35"/>
+    <row r="599" ht="15.75" customHeight="1" s="35"/>
+    <row r="600" ht="15.75" customHeight="1" s="35"/>
+    <row r="601" ht="15.75" customHeight="1" s="35"/>
+    <row r="602" ht="15.75" customHeight="1" s="35"/>
+    <row r="603" ht="15.75" customHeight="1" s="35"/>
+    <row r="604" ht="15.75" customHeight="1" s="35"/>
+    <row r="605" ht="15.75" customHeight="1" s="35"/>
+    <row r="606" ht="15.75" customHeight="1" s="35"/>
+    <row r="607" ht="15.75" customHeight="1" s="35"/>
+    <row r="608" ht="15.75" customHeight="1" s="35"/>
+    <row r="609" ht="15.75" customHeight="1" s="35"/>
+    <row r="610" ht="15.75" customHeight="1" s="35"/>
+    <row r="611" ht="15.75" customHeight="1" s="35"/>
+    <row r="612" ht="15.75" customHeight="1" s="35"/>
+    <row r="613" ht="15.75" customHeight="1" s="35"/>
+    <row r="614" ht="15.75" customHeight="1" s="35"/>
+    <row r="615" ht="15.75" customHeight="1" s="35"/>
+    <row r="616" ht="15.75" customHeight="1" s="35"/>
+    <row r="617" ht="15.75" customHeight="1" s="35"/>
+    <row r="618" ht="15.75" customHeight="1" s="35"/>
+    <row r="619" ht="15.75" customHeight="1" s="35"/>
+    <row r="620" ht="15.75" customHeight="1" s="35"/>
+    <row r="621" ht="15.75" customHeight="1" s="35"/>
+    <row r="622" ht="15.75" customHeight="1" s="35"/>
+    <row r="623" ht="15.75" customHeight="1" s="35"/>
+    <row r="624" ht="15.75" customHeight="1" s="35"/>
+    <row r="625" ht="15.75" customHeight="1" s="35"/>
+    <row r="626" ht="15.75" customHeight="1" s="35"/>
+    <row r="627" ht="15.75" customHeight="1" s="35"/>
+    <row r="628" ht="15.75" customHeight="1" s="35"/>
+    <row r="629" ht="15.75" customHeight="1" s="35"/>
+    <row r="630" ht="15.75" customHeight="1" s="35"/>
+    <row r="631" ht="15.75" customHeight="1" s="35"/>
+    <row r="632" ht="15.75" customHeight="1" s="35"/>
+    <row r="633" ht="15.75" customHeight="1" s="35"/>
+    <row r="634" ht="15.75" customHeight="1" s="35"/>
+    <row r="635" ht="15.75" customHeight="1" s="35"/>
+    <row r="636" ht="15.75" customHeight="1" s="35"/>
+    <row r="637" ht="15.75" customHeight="1" s="35"/>
+    <row r="638" ht="15.75" customHeight="1" s="35"/>
+    <row r="639" ht="15.75" customHeight="1" s="35"/>
+    <row r="640" ht="15.75" customHeight="1" s="35"/>
+    <row r="641" ht="15.75" customHeight="1" s="35"/>
+    <row r="642" ht="15.75" customHeight="1" s="35"/>
+    <row r="643" ht="15.75" customHeight="1" s="35"/>
+    <row r="644" ht="15.75" customHeight="1" s="35"/>
+    <row r="645" ht="15.75" customHeight="1" s="35"/>
+    <row r="646" ht="15.75" customHeight="1" s="35"/>
+    <row r="647" ht="15.75" customHeight="1" s="35"/>
+    <row r="648" ht="15.75" customHeight="1" s="35"/>
+    <row r="649" ht="15.75" customHeight="1" s="35"/>
+    <row r="650" ht="15.75" customHeight="1" s="35"/>
+    <row r="651" ht="15.75" customHeight="1" s="35"/>
+    <row r="652" ht="15.75" customHeight="1" s="35"/>
+    <row r="653" ht="15.75" customHeight="1" s="35"/>
+    <row r="654" ht="15.75" customHeight="1" s="35"/>
+    <row r="655" ht="15.75" customHeight="1" s="35"/>
+    <row r="656" ht="15.75" customHeight="1" s="35"/>
+    <row r="657" ht="15.75" customHeight="1" s="35"/>
+    <row r="658" ht="15.75" customHeight="1" s="35"/>
+    <row r="659" ht="15.75" customHeight="1" s="35"/>
+    <row r="660" ht="15.75" customHeight="1" s="35"/>
+    <row r="661" ht="15.75" customHeight="1" s="35"/>
+    <row r="662" ht="15.75" customHeight="1" s="35"/>
+    <row r="663" ht="15.75" customHeight="1" s="35"/>
+    <row r="664" ht="15.75" customHeight="1" s="35"/>
+    <row r="665" ht="15.75" customHeight="1" s="35"/>
+    <row r="666" ht="15.75" customHeight="1" s="35"/>
+    <row r="667" ht="15.75" customHeight="1" s="35"/>
+    <row r="668" ht="15.75" customHeight="1" s="35"/>
+    <row r="669" ht="15.75" customHeight="1" s="35"/>
+    <row r="670" ht="15.75" customHeight="1" s="35"/>
+    <row r="671" ht="15.75" customHeight="1" s="35"/>
+    <row r="672" ht="15.75" customHeight="1" s="35"/>
+    <row r="673" ht="15.75" customHeight="1" s="35"/>
+    <row r="674" ht="15.75" customHeight="1" s="35"/>
+    <row r="675" ht="15.75" customHeight="1" s="35"/>
+    <row r="676" ht="15.75" customHeight="1" s="35"/>
+    <row r="677" ht="15.75" customHeight="1" s="35"/>
+    <row r="678" ht="15.75" customHeight="1" s="35"/>
+    <row r="679" ht="15.75" customHeight="1" s="35"/>
+    <row r="680" ht="15.75" customHeight="1" s="35"/>
+    <row r="681" ht="15.75" customHeight="1" s="35"/>
+    <row r="682" ht="15.75" customHeight="1" s="35"/>
+    <row r="683" ht="15.75" customHeight="1" s="35"/>
+    <row r="684" ht="15.75" customHeight="1" s="35"/>
+    <row r="685" ht="15.75" customHeight="1" s="35"/>
+    <row r="686" ht="15.75" customHeight="1" s="35"/>
+    <row r="687" ht="15.75" customHeight="1" s="35"/>
+    <row r="688" ht="15.75" customHeight="1" s="35"/>
+    <row r="689" ht="15.75" customHeight="1" s="35"/>
+    <row r="690" ht="15.75" customHeight="1" s="35"/>
+    <row r="691" ht="15.75" customHeight="1" s="35"/>
+    <row r="692" ht="15.75" customHeight="1" s="35"/>
+    <row r="693" ht="15.75" customHeight="1" s="35"/>
+    <row r="694" ht="15.75" customHeight="1" s="35"/>
+    <row r="695" ht="15.75" customHeight="1" s="35"/>
+    <row r="696" ht="15.75" customHeight="1" s="35"/>
+    <row r="697" ht="15.75" customHeight="1" s="35"/>
+    <row r="698" ht="15.75" customHeight="1" s="35"/>
+    <row r="699" ht="15.75" customHeight="1" s="35"/>
+    <row r="700" ht="15.75" customHeight="1" s="35"/>
+    <row r="701" ht="15.75" customHeight="1" s="35"/>
+    <row r="702" ht="15.75" customHeight="1" s="35"/>
+    <row r="703" ht="15.75" customHeight="1" s="35"/>
+    <row r="704" ht="15.75" customHeight="1" s="35"/>
+    <row r="705" ht="15.75" customHeight="1" s="35"/>
+    <row r="706" ht="15.75" customHeight="1" s="35"/>
+    <row r="707" ht="15.75" customHeight="1" s="35"/>
+    <row r="708" ht="15.75" customHeight="1" s="35"/>
+    <row r="709" ht="15.75" customHeight="1" s="35"/>
+    <row r="710" ht="15.75" customHeight="1" s="35"/>
+    <row r="711" ht="15.75" customHeight="1" s="35"/>
+    <row r="712" ht="15.75" customHeight="1" s="35"/>
+    <row r="713" ht="15.75" customHeight="1" s="35"/>
+    <row r="714" ht="15.75" customHeight="1" s="35"/>
+    <row r="715" ht="15.75" customHeight="1" s="35"/>
+    <row r="716" ht="15.75" customHeight="1" s="35"/>
+    <row r="717" ht="15.75" customHeight="1" s="35"/>
+    <row r="718" ht="15.75" customHeight="1" s="35"/>
+    <row r="719" ht="15.75" customHeight="1" s="35"/>
+    <row r="720" ht="15.75" customHeight="1" s="35"/>
+    <row r="721" ht="15.75" customHeight="1" s="35"/>
+    <row r="722" ht="15.75" customHeight="1" s="35"/>
+    <row r="723" ht="15.75" customHeight="1" s="35"/>
+    <row r="724" ht="15.75" customHeight="1" s="35"/>
+    <row r="725" ht="15.75" customHeight="1" s="35"/>
+    <row r="726" ht="15.75" customHeight="1" s="35"/>
+    <row r="727" ht="15.75" customHeight="1" s="35"/>
+    <row r="728" ht="15.75" customHeight="1" s="35"/>
+    <row r="729" ht="15.75" customHeight="1" s="35"/>
+    <row r="730" ht="15.75" customHeight="1" s="35"/>
+    <row r="731" ht="15.75" customHeight="1" s="35"/>
+    <row r="732" ht="15.75" customHeight="1" s="35"/>
+    <row r="733" ht="15.75" customHeight="1" s="35"/>
+    <row r="734" ht="15.75" customHeight="1" s="35"/>
+    <row r="735" ht="15.75" customHeight="1" s="35"/>
+    <row r="736" ht="15.75" customHeight="1" s="35"/>
+    <row r="737" ht="15.75" customHeight="1" s="35"/>
+    <row r="738" ht="15.75" customHeight="1" s="35"/>
+    <row r="739" ht="15.75" customHeight="1" s="35"/>
+    <row r="740" ht="15.75" customHeight="1" s="35"/>
+    <row r="741" ht="15.75" customHeight="1" s="35"/>
+    <row r="742" ht="15.75" customHeight="1" s="35"/>
+    <row r="743" ht="15.75" customHeight="1" s="35"/>
+    <row r="744" ht="15.75" customHeight="1" s="35"/>
+    <row r="745" ht="15.75" customHeight="1" s="35"/>
+    <row r="746" ht="15.75" customHeight="1" s="35"/>
+    <row r="747" ht="15.75" customHeight="1" s="35"/>
+    <row r="748" ht="15.75" customHeight="1" s="35"/>
+    <row r="749" ht="15.75" customHeight="1" s="35"/>
+    <row r="750" ht="15.75" customHeight="1" s="35"/>
+    <row r="751" ht="15.75" customHeight="1" s="35"/>
+    <row r="752" ht="15.75" customHeight="1" s="35"/>
+    <row r="753" ht="15.75" customHeight="1" s="35"/>
+    <row r="754" ht="15.75" customHeight="1" s="35"/>
+    <row r="755" ht="15.75" customHeight="1" s="35"/>
+    <row r="756" ht="15.75" customHeight="1" s="35"/>
+    <row r="757" ht="15.75" customHeight="1" s="35"/>
+    <row r="758" ht="15.75" customHeight="1" s="35"/>
+    <row r="759" ht="15.75" customHeight="1" s="35"/>
+    <row r="760" ht="15.75" customHeight="1" s="35"/>
+    <row r="761" ht="15.75" customHeight="1" s="35"/>
+    <row r="762" ht="15.75" customHeight="1" s="35"/>
+    <row r="763" ht="15.75" customHeight="1" s="35"/>
+    <row r="764" ht="15.75" customHeight="1" s="35"/>
+    <row r="765" ht="15.75" customHeight="1" s="35"/>
+    <row r="766" ht="15.75" customHeight="1" s="35"/>
+    <row r="767" ht="15.75" customHeight="1" s="35"/>
+    <row r="768" ht="15.75" customHeight="1" s="35"/>
+    <row r="769" ht="15.75" customHeight="1" s="35"/>
+    <row r="770" ht="15.75" customHeight="1" s="35"/>
+    <row r="771" ht="15.75" customHeight="1" s="35"/>
+    <row r="772" ht="15.75" customHeight="1" s="35"/>
+    <row r="773" ht="15.75" customHeight="1" s="35"/>
+    <row r="774" ht="15.75" customHeight="1" s="35"/>
+    <row r="775" ht="15.75" customHeight="1" s="35"/>
+    <row r="776" ht="15.75" customHeight="1" s="35"/>
+    <row r="777" ht="15.75" customHeight="1" s="35"/>
+    <row r="778" ht="15.75" customHeight="1" s="35"/>
+    <row r="779" ht="15.75" customHeight="1" s="35"/>
+    <row r="780" ht="15.75" customHeight="1" s="35"/>
+    <row r="781" ht="15.75" customHeight="1" s="35"/>
+    <row r="782" ht="15.75" customHeight="1" s="35"/>
+    <row r="783" ht="15.75" customHeight="1" s="35"/>
+    <row r="784" ht="15.75" customHeight="1" s="35"/>
+    <row r="785" ht="15.75" customHeight="1" s="35"/>
+    <row r="786" ht="15.75" customHeight="1" s="35"/>
+    <row r="787" ht="15.75" customHeight="1" s="35"/>
+    <row r="788" ht="15.75" customHeight="1" s="35"/>
+    <row r="789" ht="15.75" customHeight="1" s="35"/>
+    <row r="790" ht="15.75" customHeight="1" s="35"/>
+    <row r="791" ht="15.75" customHeight="1" s="35"/>
+    <row r="792" ht="15.75" customHeight="1" s="35"/>
+    <row r="793" ht="15.75" customHeight="1" s="35"/>
+    <row r="794" ht="15.75" customHeight="1" s="35"/>
+    <row r="795" ht="15.75" customHeight="1" s="35"/>
+    <row r="796" ht="15.75" customHeight="1" s="35"/>
+    <row r="797" ht="15.75" customHeight="1" s="35"/>
+    <row r="798" ht="15.75" customHeight="1" s="35"/>
+    <row r="799" ht="15.75" customHeight="1" s="35"/>
+    <row r="800" ht="15.75" customHeight="1" s="35"/>
+    <row r="801" ht="15.75" customHeight="1" s="35"/>
+    <row r="802" ht="15.75" customHeight="1" s="35"/>
+    <row r="803" ht="15.75" customHeight="1" s="35"/>
+    <row r="804" ht="15.75" customHeight="1" s="35"/>
+    <row r="805" ht="15.75" customHeight="1" s="35"/>
+    <row r="806" ht="15.75" customHeight="1" s="35"/>
+    <row r="807" ht="15.75" customHeight="1" s="35"/>
+    <row r="808" ht="15.75" customHeight="1" s="35"/>
+    <row r="809" ht="15.75" customHeight="1" s="35"/>
+    <row r="810" ht="15.75" customHeight="1" s="35"/>
+    <row r="811" ht="15.75" customHeight="1" s="35"/>
+    <row r="812" ht="15.75" customHeight="1" s="35"/>
+    <row r="813" ht="15.75" customHeight="1" s="35"/>
+    <row r="814" ht="15.75" customHeight="1" s="35"/>
+    <row r="815" ht="15.75" customHeight="1" s="35"/>
+    <row r="816" ht="15.75" customHeight="1" s="35"/>
+    <row r="817" ht="15.75" customHeight="1" s="35"/>
+    <row r="818" ht="15.75" customHeight="1" s="35"/>
+    <row r="819" ht="15.75" customHeight="1" s="35"/>
+    <row r="820" ht="15.75" customHeight="1" s="35"/>
+    <row r="821" ht="15.75" customHeight="1" s="35"/>
+    <row r="822" ht="15.75" customHeight="1" s="35"/>
+    <row r="823" ht="15.75" customHeight="1" s="35"/>
+    <row r="824" ht="15.75" customHeight="1" s="35"/>
+    <row r="825" ht="15.75" customHeight="1" s="35"/>
+    <row r="826" ht="15.75" customHeight="1" s="35"/>
+    <row r="827" ht="15.75" customHeight="1" s="35"/>
+    <row r="828" ht="15.75" customHeight="1" s="35"/>
+    <row r="829" ht="15.75" customHeight="1" s="35"/>
+    <row r="830" ht="15.75" customHeight="1" s="35"/>
+    <row r="831" ht="15.75" customHeight="1" s="35"/>
+    <row r="832" ht="15.75" customHeight="1" s="35"/>
+    <row r="833" ht="15.75" customHeight="1" s="35"/>
+    <row r="834" ht="15.75" customHeight="1" s="35"/>
+    <row r="835" ht="15.75" customHeight="1" s="35"/>
+    <row r="836" ht="15.75" customHeight="1" s="35"/>
+    <row r="837" ht="15.75" customHeight="1" s="35"/>
+    <row r="838" ht="15.75" customHeight="1" s="35"/>
+    <row r="839" ht="15.75" customHeight="1" s="35"/>
+    <row r="840" ht="15.75" customHeight="1" s="35"/>
+    <row r="841" ht="15.75" customHeight="1" s="35"/>
+    <row r="842" ht="15.75" customHeight="1" s="35"/>
+    <row r="843" ht="15.75" customHeight="1" s="35"/>
+    <row r="844" ht="15.75" customHeight="1" s="35"/>
+    <row r="845" ht="15.75" customHeight="1" s="35"/>
+    <row r="846" ht="15.75" customHeight="1" s="35"/>
+    <row r="847" ht="15.75" customHeight="1" s="35"/>
+    <row r="848" ht="15.75" customHeight="1" s="35"/>
+    <row r="849" ht="15.75" customHeight="1" s="35"/>
+    <row r="850" ht="15.75" customHeight="1" s="35"/>
+    <row r="851" ht="15.75" customHeight="1" s="35"/>
+    <row r="852" ht="15.75" customHeight="1" s="35"/>
+    <row r="853" ht="15.75" customHeight="1" s="35"/>
+    <row r="854" ht="15.75" customHeight="1" s="35"/>
+    <row r="855" ht="15.75" customHeight="1" s="35"/>
+    <row r="856" ht="15.75" customHeight="1" s="35"/>
+    <row r="857" ht="15.75" customHeight="1" s="35"/>
+    <row r="858" ht="15.75" customHeight="1" s="35"/>
+    <row r="859" ht="15.75" customHeight="1" s="35"/>
+    <row r="860" ht="15.75" customHeight="1" s="35"/>
+    <row r="861" ht="15.75" customHeight="1" s="35"/>
+    <row r="862" ht="15.75" customHeight="1" s="35"/>
+    <row r="863" ht="15.75" customHeight="1" s="35"/>
+    <row r="864" ht="15.75" customHeight="1" s="35"/>
+    <row r="865" ht="15.75" customHeight="1" s="35"/>
+    <row r="866" ht="15.75" customHeight="1" s="35"/>
+    <row r="867" ht="15.75" customHeight="1" s="35"/>
+    <row r="868" ht="15.75" customHeight="1" s="35"/>
+    <row r="869" ht="15.75" customHeight="1" s="35"/>
+    <row r="870" ht="15.75" customHeight="1" s="35"/>
+    <row r="871" ht="15.75" customHeight="1" s="35"/>
+    <row r="872" ht="15.75" customHeight="1" s="35"/>
+    <row r="873" ht="15.75" customHeight="1" s="35"/>
+    <row r="874" ht="15.75" customHeight="1" s="35"/>
+    <row r="875" ht="15.75" customHeight="1" s="35"/>
+    <row r="876" ht="15.75" customHeight="1" s="35"/>
+    <row r="877" ht="15.75" customHeight="1" s="35"/>
+    <row r="878" ht="15.75" customHeight="1" s="35"/>
+    <row r="879" ht="15.75" customHeight="1" s="35"/>
+    <row r="880" ht="15.75" customHeight="1" s="35"/>
+    <row r="881" ht="15.75" customHeight="1" s="35"/>
+    <row r="882" ht="15.75" customHeight="1" s="35"/>
+    <row r="883" ht="15.75" customHeight="1" s="35"/>
+    <row r="884" ht="15.75" customHeight="1" s="35"/>
+    <row r="885" ht="15.75" customHeight="1" s="35"/>
+    <row r="886" ht="15.75" customHeight="1" s="35"/>
+    <row r="887" ht="15.75" customHeight="1" s="35"/>
+    <row r="888" ht="15.75" customHeight="1" s="35"/>
+    <row r="889" ht="15.75" customHeight="1" s="35"/>
+    <row r="890" ht="15.75" customHeight="1" s="35"/>
+    <row r="891" ht="15.75" customHeight="1" s="35"/>
+    <row r="892" ht="15.75" customHeight="1" s="35"/>
+    <row r="893" ht="15.75" customHeight="1" s="35"/>
+    <row r="894" ht="15.75" customHeight="1" s="35"/>
+    <row r="895" ht="15.75" customHeight="1" s="35"/>
+    <row r="896" ht="15.75" customHeight="1" s="35"/>
+    <row r="897" ht="15.75" customHeight="1" s="35"/>
+    <row r="898" ht="15.75" customHeight="1" s="35"/>
+    <row r="899" ht="15.75" customHeight="1" s="35"/>
+    <row r="900" ht="15.75" customHeight="1" s="35"/>
+    <row r="901" ht="15.75" customHeight="1" s="35"/>
+    <row r="902" ht="15.75" customHeight="1" s="35"/>
+    <row r="903" ht="15.75" customHeight="1" s="35"/>
+    <row r="904" ht="15.75" customHeight="1" s="35"/>
+    <row r="905" ht="15.75" customHeight="1" s="35"/>
+    <row r="906" ht="15.75" customHeight="1" s="35"/>
+    <row r="907" ht="15.75" customHeight="1" s="35"/>
+    <row r="908" ht="15.75" customHeight="1" s="35"/>
+    <row r="909" ht="15.75" customHeight="1" s="35"/>
+    <row r="910" ht="15.75" customHeight="1" s="35"/>
+    <row r="911" ht="15.75" customHeight="1" s="35"/>
+    <row r="912" ht="15.75" customHeight="1" s="35"/>
+    <row r="913" ht="15.75" customHeight="1" s="35"/>
+    <row r="914" ht="15.75" customHeight="1" s="35"/>
+    <row r="915" ht="15.75" customHeight="1" s="35"/>
+    <row r="916" ht="15.75" customHeight="1" s="35"/>
+    <row r="917" ht="15.75" customHeight="1" s="35"/>
+    <row r="918" ht="15.75" customHeight="1" s="35"/>
+    <row r="919" ht="15.75" customHeight="1" s="35"/>
+    <row r="920" ht="15.75" customHeight="1" s="35"/>
+    <row r="921" ht="15.75" customHeight="1" s="35"/>
+    <row r="922" ht="15.75" customHeight="1" s="35"/>
+    <row r="923" ht="15.75" customHeight="1" s="35"/>
+    <row r="924" ht="15.75" customHeight="1" s="35"/>
+    <row r="925" ht="15.75" customHeight="1" s="35"/>
+    <row r="926" ht="15.75" customHeight="1" s="35"/>
+    <row r="927" ht="15.75" customHeight="1" s="35"/>
+    <row r="928" ht="15.75" customHeight="1" s="35"/>
+    <row r="929" ht="15.75" customHeight="1" s="35"/>
+    <row r="930" ht="15.75" customHeight="1" s="35"/>
+    <row r="931" ht="15.75" customHeight="1" s="35"/>
+    <row r="932" ht="15.75" customHeight="1" s="35"/>
+    <row r="933" ht="15.75" customHeight="1" s="35"/>
+    <row r="934" ht="15.75" customHeight="1" s="35"/>
+    <row r="935" ht="15.75" customHeight="1" s="35"/>
+    <row r="936" ht="15.75" customHeight="1" s="35"/>
+    <row r="937" ht="15.75" customHeight="1" s="35"/>
+    <row r="938" ht="15.75" customHeight="1" s="35"/>
+    <row r="939" ht="15.75" customHeight="1" s="35"/>
+    <row r="940" ht="15.75" customHeight="1" s="35"/>
+    <row r="941" ht="15.75" customHeight="1" s="35"/>
+    <row r="942" ht="15.75" customHeight="1" s="35"/>
+    <row r="943" ht="15.75" customHeight="1" s="35"/>
+    <row r="944" ht="15.75" customHeight="1" s="35"/>
+    <row r="945" ht="15.75" customHeight="1" s="35"/>
+    <row r="946" ht="15.75" customHeight="1" s="35"/>
+    <row r="947" ht="15.75" customHeight="1" s="35"/>
+    <row r="948" ht="15.75" customHeight="1" s="35"/>
+    <row r="949" ht="15.75" customHeight="1" s="35"/>
+    <row r="950" ht="15.75" customHeight="1" s="35"/>
+    <row r="951" ht="15.75" customHeight="1" s="35"/>
+    <row r="952" ht="15.75" customHeight="1" s="35"/>
+    <row r="953" ht="15.75" customHeight="1" s="35"/>
+    <row r="954" ht="15.75" customHeight="1" s="35"/>
+    <row r="955" ht="15.75" customHeight="1" s="35"/>
+    <row r="956" ht="15.75" customHeight="1" s="35"/>
+    <row r="957" ht="15.75" customHeight="1" s="35"/>
+    <row r="958" ht="15.75" customHeight="1" s="35"/>
+    <row r="959" ht="15.75" customHeight="1" s="35"/>
+    <row r="960" ht="15.75" customHeight="1" s="35"/>
+    <row r="961" ht="15.75" customHeight="1" s="35"/>
+    <row r="962" ht="15.75" customHeight="1" s="35"/>
+    <row r="963" ht="15.75" customHeight="1" s="35"/>
+    <row r="964" ht="15.75" customHeight="1" s="35"/>
+    <row r="965" ht="15.75" customHeight="1" s="35"/>
+    <row r="966" ht="15.75" customHeight="1" s="35"/>
+    <row r="967" ht="15.75" customHeight="1" s="35"/>
+    <row r="968" ht="15.75" customHeight="1" s="35"/>
+    <row r="969" ht="15.75" customHeight="1" s="35"/>
+    <row r="970" ht="15.75" customHeight="1" s="35"/>
+    <row r="971" ht="15.75" customHeight="1" s="35"/>
+    <row r="972" ht="15.75" customHeight="1" s="35"/>
+    <row r="973" ht="15.75" customHeight="1" s="35"/>
+    <row r="974" ht="15.75" customHeight="1" s="35"/>
+    <row r="975" ht="15.75" customHeight="1" s="35"/>
+    <row r="976" ht="15.75" customHeight="1" s="35"/>
+    <row r="977" ht="15.75" customHeight="1" s="35"/>
+    <row r="978" ht="15.75" customHeight="1" s="35"/>
+    <row r="979" ht="15.75" customHeight="1" s="35"/>
+    <row r="980" ht="15.75" customHeight="1" s="35"/>
+    <row r="981" ht="15.75" customHeight="1" s="35"/>
+    <row r="982" ht="15.75" customHeight="1" s="35"/>
+    <row r="983" ht="15.75" customHeight="1" s="35"/>
+    <row r="984" ht="15.75" customHeight="1" s="35"/>
+    <row r="985" ht="15.75" customHeight="1" s="35"/>
+    <row r="986" ht="15.75" customHeight="1" s="35"/>
+    <row r="987" ht="15.75" customHeight="1" s="35"/>
+    <row r="988" ht="15.75" customHeight="1" s="35"/>
+    <row r="989" ht="15.75" customHeight="1" s="35"/>
+    <row r="990" ht="15.75" customHeight="1" s="35"/>
+    <row r="991" ht="15.75" customHeight="1" s="35"/>
+    <row r="992" ht="15.75" customHeight="1" s="35"/>
+    <row r="993" ht="15.75" customHeight="1" s="35"/>
+    <row r="994" ht="15.75" customHeight="1" s="35"/>
+    <row r="995" ht="15.75" customHeight="1" s="35"/>
+    <row r="996" ht="15.75" customHeight="1" s="35"/>
+    <row r="997" ht="15.75" customHeight="1" s="35"/>
+    <row r="998" ht="15.75" customHeight="1" s="35"/>
+    <row r="999" ht="15.75" customHeight="1" s="35"/>
+    <row r="1000" ht="15.75" customHeight="1" s="35"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" style="35" min="1" max="1"/>
+    <col width="75" customWidth="1" style="35" min="2" max="2"/>
+    <col width="40" customWidth="1" style="35" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="40" t="inlineStr">
+        <is>
+          <t>Question / ambiguity for the PO or developer</t>
+        </is>
+      </c>
+      <c r="C1" s="40" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="125.5" customHeight="1" s="35">
+      <c r="A2" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): src/app/events/[id]/page.tsx crashed for an Attendee viewing a confirmed, registration-open event, because it unconditionally read `event.facilityRequirements.length` while src/lib/permissions.ts's ATTENDEE_EVENT_FIELDS omits that field entirely for an Attendee (it's internal planning information, docs/PERMISSIONS.md §4). Fixed by treating facilityRequirements as optional and guarding the read, rather than adding it to what an Attendee's response includes — that would have leaked internal information the policy deliberately withholds. See SPM-31-TC09 (now Positive) and SPM-31-TC14.</t>
+        </is>
+      </c>
+      <c r="C2" s="41" t="n"/>
+    </row>
+    <row r="3" ht="98.5" customHeight="1" s="35">
+      <c r="A3" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): the coordinator's name must be shown tagged to the event on the Overview tab itself (SPM-31-TC12, SPM-31-TC13), not only in the Equipment tab's 'Event at a glance' sidebar. This applies for every role that can already see the coordinator in the API response today (everyone except Attendee — see docs/PERMISSIONS.md's internal-planning-information list); Attendee continues to never see it (SPM-31-TC14).</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="n"/>
+    </row>
+    <row r="4" ht="152.5" customHeight="1" s="35">
+      <c r="A4" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): the Overview tab must also show who organised the event and their company. Internal roles and the Organiser themselves see both 'Organiser' (personal name) and 'Company' (SPM-31-TC01, TC03, TC04). An Attendee sees 'Company' only, never 'Organiser' (SPM-31-TC09, TC14) — this changes docs/PERMISSIONS.md's stated policy that organiser/client identity is withheld entirely from Attendee; the company name is now a deliberate exception, but the organiser's personal name stays withheld. Implemented by fetching the event's own `organisation` relation separately from `organiser.organisation` (src/app/api/events/[id]/route.ts), since the two can differ (see the schema's own note on Event.organisationId vs a user's organisationId).</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="n"/>
+    </row>
+    <row r="5" ht="98.5" customHeight="1" s="35">
+      <c r="A5" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): Category and Preferred layout must render capitalised and human-readable (e.g. 'conference' → 'Conference'), not as the raw stored value, matching how Status already displays. Implemented by exporting and reusing statuses.ts's existing `humanise()` helper rather than duplicating it. Verified visually during manual testing rather than as its own dedicated test case (a formatting-only change, removed from the suite per user request 2026-09-22).</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="n"/>
+    </row>
+    <row r="6" ht="139" customHeight="1" s="35">
+      <c r="A6" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): there is no Overview view for a draft at all - only a submitted event has one. Found because the original TC03 described the info banner on the Overview tab for a draft, but 'My Events' actually routes a draft straight to the edit form (src/app/events/[id]/edit/page.tsx, which has no tabs and no link back to Overview), so that banner was only ever reachable by typing the URL directly. Fixed by redirecting the Overview page to '/events/{id}/edit' whenever the fetched event's status is 'draft', and removing the now-dead draft-banner code (src/app/events/[id]/page.tsx). See SPM-31-TC03 (rewritten) and SPM-31-TC15.</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="n"/>
+    </row>
+    <row r="7" ht="112" customHeight="1" s="35">
+      <c r="A7" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): added a visible, auto-generated reference number (Event.sequenceNumber, formatted as 'EVT-000123' by eventReference() in src/lib/format.ts) shown to every role including Attendee, next to the event's title. This is distinct from Event.id (an opaque UUID, changes on every reseed) and Event.seedKey (internal, seed-data only, never shown in the UI) - it exists specifically so frontend users have something durable and human-readable to refer to an event by. Migration 20260922213000_add_event_sequence_number. See SPM-31-TC16.</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="n"/>
+    </row>
+    <row r="8" ht="166" customHeight="1" s="35">
+      <c r="A8" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): the event's web address itself now uses this reference (e.g. /events/EVT-000005) instead of the underlying UUID. GET/PATCH /api/events/[id] resolve the route segment via parseEventReference() + a lookup by sequenceNumber (src/lib/format.ts, src/app/api/events/[id]/route.ts); the equipment sub-routes and src/lib/apiAuth.ts's new resolveEventId() do the same. Every internal link-building site (events list, dashboard, new-event redirect, tab links) was updated to build the reference rather than use the raw id. This is a bigger, cross-cutting change than SPM-31's original scope - it affects every story that touches an event's URL, not just this one - so it needs surfacing to the team before merging, not just landing quietly. See SPM-31-TC17, TC18.</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="n"/>
+    </row>
+    <row r="9" ht="125.5" customHeight="1" s="35">
+      <c r="A9" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>RESOLVED (2026-09-22): an Attendee's Overview view is now a genuinely curated subset, not the same three-card layout as every other role with most fields showing '—'. 'Expected attendance', 'Preferred layout', 'Accessibility notes' and 'Special requirements' are now optional on EventDetail (src/app/events/[id]/page.tsx) and each row/card renders only when the field is actually present in the API response, exactly like Organiser/Coordinator/Company already did. The whole 'Venue requirements' card is hidden entirely for an Attendee, rather than shown with every field blank. See SPM-31-TC09, TC14, TC19.</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="24.75" customWidth="1" style="35" min="1" max="1"/>
+    <col width="56.75" customWidth="1" style="35" min="2" max="2"/>
+    <col width="12.63" customWidth="1" style="35" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="35">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="35">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30.75" customHeight="1" s="35">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="35">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Open 'All Events'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="35">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Events list page</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="57.75" customHeight="1" s="35">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Every row shows a 'Reference' column (e.g. 'EVT-000005') alongside Event, When, Attendance and Status.
+Clicking a row opens that event at the web address matching its reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="35">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="35">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="35"/>
+    <row r="10" ht="15.75" customHeight="1" s="35">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="35">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Every row shows a 'Reference' column (e.g. 'EVT-000005') alongside Event, When, Attendance and Status.
+Clicking a row opens that event at the web address matching its reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="35">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="35">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="35">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="35">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="35"/>
+    <row r="17" ht="15.75" customHeight="1" s="35"/>
+    <row r="18" ht="15.75" customHeight="1" s="35">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="35">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>Every row shows a 'Reference' column (e.g. 'EVT-000200') alongside Event, When, Attendance and Status.
+Clicking a row opens that event at the web address matching its reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="35">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="35">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="35">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="35">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="35"/>
+    <row r="25" ht="15.75" customHeight="1" s="35"/>
+    <row r="26" ht="15.75" customHeight="1" s="35"/>
+    <row r="27" ht="15.75" customHeight="1" s="35"/>
+    <row r="28" ht="15.75" customHeight="1" s="35"/>
+    <row r="29" ht="15.75" customHeight="1" s="35"/>
+    <row r="30" ht="15.75" customHeight="1" s="35"/>
     <row r="31" ht="15.75" customHeight="1" s="35"/>
     <row r="32" ht="15.75" customHeight="1" s="35"/>
     <row r="33" ht="15.75" customHeight="1" s="35"/>
@@ -16105,7 +16167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -16268,7 +16330,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16389,7 +16451,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -16546,7 +16608,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -17543,7 +17605,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="35" min="1" max="1"/>
@@ -17565,9 +17627,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC02</t>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC01</t>
         </is>
       </c>
     </row>
@@ -17577,47 +17639,48 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff — not the coordinator, organiser, or attendee of any specific event.
-'Pearl Delta Safety Conference' (status Planning, coordinator Hui Shan Neo) exists.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Daniel Tan (daniel.tan@connectsphere.com / password123), Event Coordinator assigned to 'Meridian Wealth Management Forum' (status Confirmed, organised by James Koh, category Conference, expected attendance 150, preferred layout Theatre, registration enabled with capacity 150).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open 'All Events'
-2. Open 'Pearl Delta Safety Conference'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1" s="35">
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Open 'Meridian Wealth Management Forum' from 'All Events'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Pearl Delta Safety Conference | Viewer role: Venue Staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="35">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Meridian Wealth Management Forum</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="165.75" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000005' is shown next to the title, beside the 'Confirmed' status badge.
+The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
+The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
+The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
         </is>
       </c>
     </row>
@@ -17627,7 +17690,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17659,9 +17722,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000005' is shown next to the title, beside the 'Confirmed' status badge.
+The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
+The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
+The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
         </is>
       </c>
     </row>
@@ -17695,7 +17761,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17727,10 +17793,12 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The event opens normally and its Overview details are shown with EVT-000209
-Planning</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000200' is shown next to the title, beside the 'Confirmed' status badge.
+The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
+The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
+The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
         </is>
       </c>
     </row>
@@ -17742,7 +17810,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -17754,7 +17822,7 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>EVT-000200 shown instead of EVT-000005</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17832,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -17781,12 +17849,75 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="35"/>
-    <row r="25" ht="15.75" customHeight="1" s="35"/>
-    <row r="26" ht="15.75" customHeight="1" s="35"/>
-    <row r="27" ht="15.75" customHeight="1" s="35"/>
-    <row r="28" ht="15.75" customHeight="1" s="35"/>
-    <row r="29" ht="15.75" customHeight="1" s="35"/>
-    <row r="30" ht="15.75" customHeight="1" s="35"/>
+    <row r="25" ht="15.75" customHeight="1" s="35">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="35">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>A reference such as 'EVT-000005' is shown next to the title, beside the 'Confirmed' status badge.
+The 'Details' card shows Category 'Conference', Status 'Confirmed', the event's date/time range under 'When', Expected attendance '150', Preferred layout 'Theatre', its description, Organiser 'James Koh', Company 'Meridian Financial Group', and Coordinator 'Daniel Tan'.
+The 'Venue requirements' card shows the event's accessibility notes and special requirements (or '—' where none are recorded).
+The 'Registration' card shows Capacity '150' and the registration window, since registration is enabled for this event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="35">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="35">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Failed cases fixed by kristen on 2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="35">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B29" s="39" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="35">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>46290</v>
+      </c>
+    </row>
     <row r="31" ht="15.75" customHeight="1" s="35"/>
     <row r="32" ht="15.75" customHeight="1" s="35"/>
     <row r="33" ht="15.75" customHeight="1" s="35"/>
@@ -18791,9 +18922,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC03</t>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC02</t>
         </is>
       </c>
     </row>
@@ -18803,23 +18934,23 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), Event Organiser.
-'Q1 Investor Update (rough idea)' is her own Draft event with description 'Still checking dates with the exec team.' and no category, schedule, or attendance set yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff — not the coordinator, organiser, or attendee of any specific event.
+'Pearl Delta Safety Conference' (status Planning, coordinator Hui Shan Neo) exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>1. Open 'My Events'
-2. Click the row for 'Q1 Investor Update (rough idea)' under 'Drafts — not yet submitted'</t>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Open 'All Events'
+2. Open 'Pearl Delta Safety Conference'</t>
         </is>
       </c>
     </row>
@@ -18829,22 +18960,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Q1 Investor Update (rough idea) (Draft, owned by Rachel Ng)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.25" customHeight="1" s="35">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Pearl Delta Safety Conference | Viewer role: Venue Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>She is taken straight to the 'Edit draft' page, not an Overview tab.
-No Details card, no Organiser/Company/Coordinator rows, and no draft info banner appear anywhere — a draft has no Overview view at all; it is only ever edited, never overviewed</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
         </is>
       </c>
     </row>
@@ -18854,7 +18984,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18886,10 +19016,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>She is taken straight to the 'Edit draft' page, not an Overview tab.
-No Details card, no Organiser/Company/Coordinator rows, and no draft info banner appear anywhere — a draft has no Overview view at all; it is only ever edited, never overviewed</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
         </is>
       </c>
     </row>
@@ -18923,7 +19052,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18955,10 +19084,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>She is taken straight to the 'Edit draft' page, not an Overview tab.
-No Details card, no Organiser/Company/Coordinator rows, and no draft info banner appear anywhere — a draft has no Overview view at all; it is only ever edited, never overviewed</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The event opens normally and its Overview details are shown with EVT-000209
+Planning</t>
         </is>
       </c>
     </row>
@@ -18992,7 +19121,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -20019,35 +20148,35 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="84.75" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), Event Organiser at Meridian Financial Group.
-'Meridian Graduate Recruitment Evening' (status Submitted, category Networking, expected attendance 120, preferred layout Exhibition) was raised by her colleague James Koh, also at Meridian Financial Group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30.75" customHeight="1" s="35">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), Event Organiser.
+'Q1 Investor Update (rough idea)' is her own Draft event with description 'Still checking dates with the exec team.' and no category, schedule, or attendance set yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.25" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>1. Open 'My Events'
-2. Open 'Meridian Graduate Recruitment Evening'</t>
+2. Click the row for 'Q1 Investor Update (rough idea)' under 'Drafts — not yet submitted'</t>
         </is>
       </c>
     </row>
@@ -20057,9 +20186,9 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Event: Meridian Graduate Recruitment Evening (owned by a colleague, same organisation)</t>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Q1 Investor Update (rough idea) (Draft, owned by Rachel Ng)</t>
         </is>
       </c>
     </row>
@@ -20069,9 +20198,10 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>The event opens and shows its details (Category 'Networking', Status 'Submitted', Expected attendance '120', Preferred layout 'Exhibition', Organiser 'James Koh', Company 'Meridian Financial Group', Coordinator 'Not yet assigned') even though Rachel Ng did not raise it herself — an organiser can view their own client organisation's submitted events, not only the ones they personally created.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>She is taken straight to the 'Edit draft' page, not an Overview tab.
+No Details card, no Organiser/Company/Coordinator rows, and no draft info banner appear anywhere — a draft has no Overview view at all; it is only ever edited, never overviewed</t>
         </is>
       </c>
     </row>
@@ -20081,7 +20211,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -20113,9 +20243,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>The event opens and shows its details (Category 'Networking', Status 'Submitted', Expected attendance '120', Preferred layout 'Exhibition', Organiser 'James Koh', Company 'Meridian Financial Group', Coordinator 'Not yet assigned') even though Rachel Ng did not raise it herself — an organiser can view their own client organisation's submitted events, not only the ones they personally created.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>She is taken straight to the 'Edit draft' page, not an Overview tab.
+No Details card, no Organiser/Company/Coordinator rows, and no draft info banner appear anywhere — a draft has no Overview view at all; it is only ever edited, never overviewed</t>
         </is>
       </c>
     </row>
@@ -20149,7 +20280,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -20181,9 +20312,10 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>The event opens and shows its details (Category 'Networking', Status 'Submitted', Expected attendance '120', Preferred layout 'Exhibition', Organiser 'James Koh', Company 'Meridian Financial Group', Coordinator 'Not yet assigned') even though Rachel Ng did not raise it herself — an organiser can view their own client organisation's submitted events, not only the ones they personally created.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>She is taken straight to the 'Edit draft' page, not an Overview tab.
+No Details card, no Organiser/Company/Coordinator rows, and no draft info banner appear anywhere — a draft has no Overview view at all; it is only ever edited, never overviewed</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20349,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -21244,9 +21376,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC05</t>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC04</t>
         </is>
       </c>
     </row>
@@ -21256,24 +21388,23 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), Event Organiser at Meridian Financial Group.
- Her colleague James Koh (james.koh@meridianfina.com) has created, but not submitted, a new event request titled 'Meridian Q4 Budget Planning' (status Draft) via 'New event request'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.25" customHeight="1" s="35">
+'Meridian Graduate Recruitment Evening' (status Submitted, category Networking, expected attendance 120, preferred layout Exhibition) was raised by her colleague James Koh, also at Meridian Financial Group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>1. Note the web address of 'Meridian Q4 Budget Planning' while logged in as James Koh
- 2. Log out and log back in as Rachel Ng (rachel.ng@meridianfina.com / password123)
- 3. Navigate directly to that web address</t>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>1. Open 'My Events'
+2. Open 'Meridian Graduate Recruitment Evening'</t>
         </is>
       </c>
     </row>
@@ -21283,22 +21414,21 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>Event: Meridian Q4 Budget Planning (Draft, owned by a colleague)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Event: Meridian Graduate Recruitment Evening (owned by a colleague, same organisation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.25" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>The web address James Koh's own draft opens at is its 'Edit draft' address, so that's the address Rachel Ng lands on too.
-She sees 'Could not open this draft' with the message 'This draft could not be found. It may have been removed, or it isn't yours.' — a draft stays private to the organiser who owns it, even from a colleague at the same client organisation.</t>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>The event opens and shows its details (Category 'Networking', Status 'Submitted', Expected attendance '120', Preferred layout 'Exhibition', Organiser 'James Koh', Company 'Meridian Financial Group', Coordinator 'Not yet assigned') even though Rachel Ng did not raise it herself — an organiser can view their own client organisation's submitted events, not only the ones they personally created.</t>
         </is>
       </c>
     </row>
@@ -21308,7 +21438,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -21340,10 +21470,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>The web address James Koh's own draft opens at is its 'Edit draft' address, so that's the address Rachel Ng lands on too.
-She sees 'Could not open this draft' with the message 'This draft could not be found. It may have been removed, or it isn't yours.' — a draft stays private to the organiser who owns it, even from a colleague at the same client organisation.</t>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>The event opens and shows its details (Category 'Networking', Status 'Submitted', Expected attendance '120', Preferred layout 'Exhibition', Organiser 'James Koh', Company 'Meridian Financial Group', Coordinator 'Not yet assigned') even though Rachel Ng did not raise it herself — an organiser can view their own client organisation's submitted events, not only the ones they personally created.</t>
         </is>
       </c>
     </row>
@@ -21377,7 +21506,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -21409,10 +21538,9 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>The web address James Koh's own draft opens at is its 'Edit draft' address, so that's the address Rachel Ng lands on too.
-She sees 'Could not open this draft' with the message 'This draft could not be found. It may have been removed, or it isn't yours.' — a draft stays private to the organiser who owns it, even from a colleague at the same client organisation.</t>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>The event opens and shows its details (Category 'Networking', Status 'Submitted', Expected attendance '120', Preferred layout 'Exhibition', Organiser 'James Koh', Company 'Meridian Financial Group', Coordinator 'Not yet assigned') even though Rachel Ng did not raise it herself — an organiser can view their own client organisation's submitted events, not only the ones they personally created.</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21574,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -22473,26 +22601,26 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.25" customHeight="1" s="35">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="84.75" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>Nusantara Developer Summit' (status Submitted) belongs to Budi Santoso (budi.santoso@nusantaratec.com / password123) at Nusantara Tech Labs.
- James Koh (james.koh@meridianfina.com / password123) is an Event Organiser at Meridian Financial Group, a different client organisation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), Event Organiser at Meridian Financial Group.
+ Her colleague James Koh (james.koh@meridianfina.com) has created, but not submitted, a new event request titled 'Meridian Q4 Budget Planning' (status Draft) via 'New event request'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.25" customHeight="1" s="35">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -22500,8 +22628,8 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>1. Logged in as Budi Santoso, open 'Nusantara Developer Summit' from 'My Events' and note its web address
- 2. Log out and log in as James Koh (james.koh@meridianfina.com / password123)
+          <t>1. Note the web address of 'Meridian Q4 Budget Planning' while logged in as James Koh
+ 2. Log out and log back in as Rachel Ng (rachel.ng@meridianfina.com / password123)
  3. Navigate directly to that web address</t>
         </is>
       </c>
@@ -22514,11 +22642,11 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Event: Nusantara Developer Summit (different client organisation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1" s="35">
+          <t>Event: Meridian Q4 Budget Planning (Draft, owned by a colleague)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -22526,7 +22654,8 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.'</t>
+          <t>The web address James Koh's own draft opens at is its 'Edit draft' address, so that's the address Rachel Ng lands on too.
+She sees 'Could not open this draft' with the message 'This draft could not be found. It may have been removed, or it isn't yours.' — a draft stays private to the organiser who owns it, even from a colleague at the same client organisation.</t>
         </is>
       </c>
     </row>
@@ -22536,7 +22665,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -22570,7 +22699,8 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.'</t>
+          <t>The web address James Koh's own draft opens at is its 'Edit draft' address, so that's the address Rachel Ng lands on too.
+She sees 'Could not open this draft' with the message 'This draft could not be found. It may have been removed, or it isn't yours.' — a draft stays private to the organiser who owns it, even from a colleague at the same client organisation.</t>
         </is>
       </c>
     </row>
@@ -22604,7 +22734,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -22623,68 +22753,69 @@
     <row r="16" ht="15.75" customHeight="1" s="35"/>
     <row r="17" ht="15.75" customHeight="1" s="35"/>
     <row r="18" ht="15.75" customHeight="1" s="35">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
+      <c r="B18" s="13" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="35">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>The page shows 'Could not load this", 'This event doesn't exist, or you don't have access to it.'</t>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>The web address James Koh's own draft opens at is its 'Edit draft' address, so that's the address Rachel Ng lands on too.
+She sees 'Could not open this draft' with the message 'This draft could not be found. It may have been removed, or it isn't yours.' — a draft stays private to the organiser who owns it, even from a colleague at the same client organisation.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="35">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="35">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="35">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="35">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="17" t="n">
         <v>46290</v>
       </c>
     </row>
@@ -23699,13 +23830,13 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.25" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -23713,8 +23844,8 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>Pearl Delta Safety Conference' has status Planning (not yet Confirmed), coordinator Hui Shan Neo.
- Lee Wei Ming (lee.wei.ming@example.com / password123) is an Attendee. This event is not confirmed, so it never appears in his 'Browse Events' list — the address below has to come from somewhere else, e.g. forwarded by staff.</t>
+          <t>Nusantara Developer Summit' (status Submitted) belongs to Budi Santoso (budi.santoso@nusantaratec.com / password123) at Nusantara Tech Labs.
+ James Koh (james.koh@meridianfina.com / password123) is an Event Organiser at Meridian Financial Group, a different client organisation.</t>
         </is>
       </c>
     </row>
@@ -23726,13 +23857,13 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>1. Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), open 'Pearl Delta Safety Conference' and note its web address
- 2. Log out and log in as Lee Wei Ming (lee.wei.ming@example.com / password123)
+          <t>1. Logged in as Budi Santoso, open 'Nusantara Developer Summit' from 'My Events' and note its web address
+ 2. Log out and log in as James Koh (james.koh@meridianfina.com / password123)
  3. Navigate directly to that web address</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="35">
+    <row r="5" ht="30.75" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -23740,11 +23871,11 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Event: Pearl Delta Safety Conference (status Planning)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1" s="35">
+          <t>Event: Nusantara Developer Summit (different client organisation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -23752,7 +23883,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — an event not yet confirmed is not visible to the public.</t>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.'</t>
         </is>
       </c>
     </row>
@@ -23762,7 +23893,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -23796,7 +23927,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — an event not yet confirmed is not visible to the public.</t>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.'</t>
         </is>
       </c>
     </row>
@@ -23830,7 +23961,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -23849,68 +23980,68 @@
     <row r="16" ht="15.75" customHeight="1" s="35"/>
     <row r="17" ht="15.75" customHeight="1" s="35"/>
     <row r="18" ht="15.75" customHeight="1" s="35">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
+      <c r="B18" s="22" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="35">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>The page shows 'Could not load this', 'This event doesn't exist, or you don't have access to it.' — an event not yet confirmed is not visible to the public.</t>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>The page shows 'Could not load this", 'This event doesn't exist, or you don't have access to it.'</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="35">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="35">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="35">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="35">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="25" t="n">
         <v>46290</v>
       </c>
     </row>
@@ -24925,9 +25056,9 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>SPM-31-TC08</t>
+      <c r="B2" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC07</t>
         </is>
       </c>
     </row>
@@ -24939,8 +25070,8 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>Harbourline Claims Systems Training' has status Confirmed but registration is not enabled for it, coordinator Priya Raj.
- Anita Devi (anita.devi@example.com / password123) is an Attendee. Registration isn't open, so this event never appears in her 'Browse Events' list — the address below has to come from somewhere else, e.g. forwarded by staff.</t>
+          <t>Pearl Delta Safety Conference' has status Planning (not yet Confirmed), coordinator Hui Shan Neo.
+ Lee Wei Ming (lee.wei.ming@example.com / password123) is an Attendee. This event is not confirmed, so it never appears in his 'Browse Events' list — the address below has to come from somewhere else, e.g. forwarded by staff.</t>
         </is>
       </c>
     </row>
@@ -24952,13 +25083,13 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>1. Logged in as Priya Raj (priya.raj@connectsphere.com / password123), open 'Harbourline Claims Systems Training' and note its web address
- 2. Log out and log in as Anita Devi (anita.devi@example.com / password123)
+          <t>1. Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), open 'Pearl Delta Safety Conference' and note its web address
+ 2. Log out and log in as Lee Wei Ming (lee.wei.ming@example.com / password123)
  3. Navigate directly to that web address</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="35">
+    <row r="5" ht="17.25" customHeight="1" s="35">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -24966,11 +25097,11 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Event: Harbourline Claims Systems Training (Confirmed, registration not enabled)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57.75" customHeight="1" s="35">
+          <t>Event: Pearl Delta Safety Conference (status Planning)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -24978,7 +25109,7 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — being Confirmed is not enough on its own; the event must also be open for registration for an Attendee to view it.</t>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — an event not yet confirmed is not visible to the public.</t>
         </is>
       </c>
     </row>
@@ -24988,7 +25119,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -25022,7 +25153,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — being Confirmed is not enough on its own; the event must also be open for registration for an Attendee to view it.</t>
+          <t>The page shows 'This event doesn't exist, or you don't have access to it.' — an event not yet confirmed is not visible to the public.</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25187,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -25090,7 +25221,7 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>The page shows 'Could not load this', 'This event doesn't exist, or you don't have access to it.' — being Confirmed is not enough on its own; the event must also be open for registration for an Attendee to view it.</t>
+          <t>The page shows 'Could not load this', 'This event doesn't exist, or you don't have access to it.' — an event not yet confirmed is not visible to the public.</t>
         </is>
       </c>
     </row>
@@ -25124,7 +25255,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>

--- a/docs/test-cases/SPM-31_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-31_Test_Cases.xlsx
@@ -698,11 +698,15 @@
       </c>
       <c r="G5" s="39" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H5" s="39" t="n"/>
-      <c r="I5" s="39" t="n"/>
+      <c r="I5" s="39" t="inlineStr">
+        <is>
+          <t>#125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -18900,7 +18904,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="35" min="1" max="1"/>
@@ -18909,235 +18913,241 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="35">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-23): Venue Staff, Technical Support and the Safety Officer now see an event only from Approved onwards (SPM-94 AC2, forum #125). Pearl Delta Safety Conference is in Planning, so the steps and result are unchanged; read 'internal staff can view any non-draft event' in the expected result as 'internal staff can view any event from Approved onwards (Event Coordinators and the Event Coordinator Lead: any non-draft event)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="35">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="35">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="39" t="inlineStr">
-        <is>
-          <t>SPM-31-TC02</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="71.25" customHeight="1" s="35">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>SPM-31-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1" s="35">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Logged in as Marcus Wong (marcus.wong@connectsphere.com / password123), Venue Staff — not the coordinator, organiser, or attendee of any specific event.
 'Pearl Delta Safety Conference' (status Planning, coordinator Hui Shan Neo) exists.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30.75" customHeight="1" s="35">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="30.75" customHeight="1" s="35">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>1. Open 'All Events'
 2. Open 'Pearl Delta Safety Conference'</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30.75" customHeight="1" s="35">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>Event: Pearl Delta Safety Conference | Viewer role: Venue Staff</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="44.25" customHeight="1" s="35">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Expected Result</t>
+          <t>Test Data</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
+          <t>Event: Pearl Delta Safety Conference | Viewer role: Venue Staff</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" s="35">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Created By</t>
+          <t>Expected Result</t>
         </is>
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="35">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="35">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46287</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="35"/>
-    <row r="10" ht="15.75" customHeight="1" s="35">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="35"/>
+    <row r="11" ht="15.75" customHeight="1" s="35">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="35">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
-        </is>
-      </c>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="35">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>The event opens normally and its Overview details are shown — internal staff can view any non-draft event regardless of their own relationship to it.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="35">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="35">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="35">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="35">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>46287</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="35"/>
     <row r="17" ht="15.75" customHeight="1" s="35"/>
-    <row r="18" ht="15.75" customHeight="1" s="35">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="35"/>
+    <row r="19" ht="15.75" customHeight="1" s="35">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="35">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="35">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>The event opens normally and its Overview details are shown with EVT-000209
 Planning</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="35">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="35">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="35">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="35">
       <c r="A23" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="35">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B24" s="17" t="n">
         <v>46290</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="35"/>
     <row r="25" ht="15.75" customHeight="1" s="35"/>
     <row r="26" ht="15.75" customHeight="1" s="35"/>
     <row r="27" ht="15.75" customHeight="1" s="35"/>
